--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G15">
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G17">

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -340,7 +340,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AU19"/>
+  <dimension ref="A1:AU21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -593,22 +593,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sabah</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G2">
@@ -751,27 +751,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Lincoln Red Imps</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mjällby</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G3">
@@ -902,7 +902,7 @@
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2026-07-28 13:00:00</t>
+          <t>2026-07-28 12:00:00</t>
         </is>
       </c>
     </row>
@@ -914,12 +914,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G4">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2026-07-28 14:00:00</t>
+          <t>2026-07-28 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1077,27 +1077,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>Sabah</t>
         </is>
       </c>
       <c r="G5">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2026-07-28 14:00:00</t>
+          <t>2026-07-28 12:00:00</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Lincoln Red Imps</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thun</t>
+          <t>Mjällby</t>
         </is>
       </c>
       <c r="G6">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2026-07-28 15:00:00</t>
+          <t>2026-07-28 13:00:00</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2026-07-28 15:00:00</t>
+          <t>2026-07-28 14:00:00</t>
         </is>
       </c>
     </row>
@@ -1566,27 +1566,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Egnatia Rrogozhinë</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,13 +1613,13 @@
         </is>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q8">
         <v>0</v>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2026-07-28 15:15:00</t>
+          <t>2026-07-28 14:00:00</t>
         </is>
       </c>
     </row>
@@ -1729,7 +1729,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1744,12 +1744,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Hearts</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Thun</t>
         </is>
       </c>
       <c r="G9">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2026-07-28 15:45:00</t>
+          <t>2026-07-28 15:00:00</t>
         </is>
       </c>
     </row>
@@ -1892,27 +1892,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026/2027</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FC Avan Academy</t>
+          <t>AB</t>
         </is>
       </c>
       <c r="G10">
@@ -2043,7 +2043,7 @@
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2026-07-28 16:00:00</t>
+          <t>2026-07-28 15:00:00</t>
         </is>
       </c>
     </row>
@@ -2055,27 +2055,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Egnatia Rrogozhinë</t>
         </is>
       </c>
       <c r="G11">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2026-07-28 19:30:00</t>
+          <t>2026-07-28 15:15:00</t>
         </is>
       </c>
     </row>
@@ -2218,27 +2218,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Hearts</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="G12">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2026-07-28 19:30:00</t>
+          <t>2026-07-28 15:45:00</t>
         </is>
       </c>
     </row>
@@ -2381,27 +2381,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2026/2027</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>FC Avan Academy</t>
         </is>
       </c>
       <c r="G13">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2026-07-28 21:00:00</t>
+          <t>2026-07-28 16:00:00</t>
         </is>
       </c>
     </row>
@@ -2544,12 +2544,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G14">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>2026-07-28 21:00:00</t>
+          <t>2026-07-28 19:30:00</t>
         </is>
       </c>
     </row>
@@ -2707,12 +2707,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G15">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>2026-07-28 21:00:00</t>
+          <t>2026-07-28 19:30:00</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G17">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Fortaleza</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G18">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>2026-07-28 21:35:00</t>
+          <t>2026-07-28 21:00:00</t>
         </is>
       </c>
     </row>
@@ -3359,156 +3359,482 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Chapecoense</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Vasco da Gama</t>
+        </is>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19">
+        <v>0</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>0</v>
+      </c>
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+      <c r="S19">
+        <v>0</v>
+      </c>
+      <c r="T19">
+        <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>0</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+      <c r="AF19">
+        <v>0</v>
+      </c>
+      <c r="AG19">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+      <c r="AL19">
+        <v>0</v>
+      </c>
+      <c r="AM19">
+        <v>-1</v>
+      </c>
+      <c r="AN19">
+        <v>-1</v>
+      </c>
+      <c r="AO19">
+        <v>-1</v>
+      </c>
+      <c r="AP19">
+        <v>-1</v>
+      </c>
+      <c r="AQ19">
+        <v>0</v>
+      </c>
+      <c r="AR19">
+        <v>0</v>
+      </c>
+      <c r="AS19">
+        <v>0</v>
+      </c>
+      <c r="AT19">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2026-07-28 21:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>21:35</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Fortaleza</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Botafogo SP</t>
+        </is>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>0</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>0</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>-1</v>
+      </c>
+      <c r="AN20">
+        <v>-1</v>
+      </c>
+      <c r="AO20">
+        <v>-1</v>
+      </c>
+      <c r="AP20">
+        <v>-1</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2026-07-28 21:35:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>22:00</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Canada Canadian Premier League</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Cavalry FC</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>Supra du Québec</t>
         </is>
       </c>
-      <c r="G19">
-        <v>0</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>0</v>
-      </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19" t="inlineStr">
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
         <is>
           <t>suspended</t>
         </is>
       </c>
-      <c r="N19">
+      <c r="N21">
         <v>1.3</v>
       </c>
-      <c r="O19">
+      <c r="O21">
         <v>4.65</v>
       </c>
-      <c r="P19">
+      <c r="P21">
         <v>6.5</v>
       </c>
-      <c r="Q19">
+      <c r="Q21">
         <v>1.8</v>
       </c>
-      <c r="R19">
+      <c r="R21">
         <v>2.3</v>
       </c>
-      <c r="S19">
+      <c r="S21">
         <v>1.25</v>
       </c>
-      <c r="T19">
+      <c r="T21">
         <v>3.25</v>
       </c>
-      <c r="U19">
+      <c r="U21">
         <v>2.48</v>
       </c>
-      <c r="V19">
+      <c r="V21">
         <v>1.5</v>
       </c>
-      <c r="W19">
+      <c r="W21">
         <v>1.1</v>
       </c>
-      <c r="X19">
+      <c r="X21">
         <v>1.02</v>
       </c>
-      <c r="Y19">
+      <c r="Y21">
         <v>1.17</v>
       </c>
-      <c r="Z19">
+      <c r="Z21">
         <v>4</v>
       </c>
-      <c r="AA19">
+      <c r="AA21">
         <v>1.66</v>
       </c>
-      <c r="AB19">
+      <c r="AB21">
         <v>2.1</v>
       </c>
-      <c r="AC19">
+      <c r="AC21">
         <v>2.56</v>
       </c>
-      <c r="AD19">
+      <c r="AD21">
         <v>1.43</v>
       </c>
-      <c r="AE19">
+      <c r="AE21">
         <v>1.13</v>
       </c>
-      <c r="AF19">
+      <c r="AF21">
         <v>1.92</v>
       </c>
-      <c r="AG19">
+      <c r="AG21">
         <v>1.91</v>
       </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ21">
         <v>1.12</v>
       </c>
-      <c r="AK19">
+      <c r="AK21">
         <v>2.88</v>
       </c>
-      <c r="AL19">
-        <v>0</v>
-      </c>
-      <c r="AM19">
-        <v>-1</v>
-      </c>
-      <c r="AN19">
-        <v>-1</v>
-      </c>
-      <c r="AO19">
-        <v>-1</v>
-      </c>
-      <c r="AP19">
-        <v>-1</v>
-      </c>
-      <c r="AQ19">
-        <v>0</v>
-      </c>
-      <c r="AR19">
-        <v>0</v>
-      </c>
-      <c r="AS19">
-        <v>0</v>
-      </c>
-      <c r="AT19">
-        <v>0</v>
-      </c>
-      <c r="AU19" t="inlineStr">
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>-1</v>
+      </c>
+      <c r="AN21">
+        <v>-1</v>
+      </c>
+      <c r="AO21">
+        <v>-1</v>
+      </c>
+      <c r="AP21">
+        <v>-1</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
         <is>
           <t>2026-07-28 22:00:00</t>
         </is>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G16">
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G17">
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G18">
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G19">

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -2913,7 +2913,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N16">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N17">
@@ -3402,17 +3402,17 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q19">
         <v>0</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>3.83</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q14">
         <v>0</v>
@@ -2754,13 +2754,13 @@
         </is>
       </c>
       <c r="N15">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="Q15">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3608,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC20">
         <v>0</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Q5">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1948,10 +1948,10 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S10">
         <v>0</v>
@@ -1960,10 +1960,10 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W10">
         <v>0</v>
@@ -1972,31 +1972,31 @@
         <v>0</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,13 +2265,13 @@
         </is>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="Q12">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="T13">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="V13">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="W13">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X13">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="Z13">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="AA13">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AB13">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AC13">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AD13">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE13">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF13">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AG13">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK13">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2600,55 +2600,55 @@
         <v>1.98</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T14">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U14">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V14">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W14">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z14">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AA14">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AB14">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC14">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD14">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AE14">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF14">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG14">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK14">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2763,55 +2763,55 @@
         <v>5.91</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T15">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U15">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="V15">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W15">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z15">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AA15">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB15">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC15">
-        <v>0</v>
+        <v>4.07</v>
       </c>
       <c r="AD15">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE15">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF15">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG15">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK15">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL15">
         <v>0</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.58</v>
+        <v>3.19</v>
       </c>
       <c r="O7">
-        <v>3.42</v>
+        <v>3.55</v>
       </c>
       <c r="P7">
-        <v>2.55</v>
+        <v>2.09</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AB7">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC7">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AD7">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF7">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG7">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK7">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.19</v>
+        <v>2.58</v>
       </c>
       <c r="O8">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="P8">
-        <v>2.09</v>
+        <v>2.55</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.83</v>
+        <v>1.58</v>
       </c>
       <c r="O14">
-        <v>3.25</v>
+        <v>3.68</v>
       </c>
       <c r="P14">
-        <v>1.98</v>
+        <v>5.91</v>
       </c>
       <c r="Q14">
-        <v>4.2</v>
+        <v>2.15</v>
       </c>
       <c r="R14">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="S14">
         <v>1.44</v>
       </c>
       <c r="T14">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="U14">
-        <v>3.3</v>
+        <v>3.27</v>
       </c>
       <c r="V14">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W14">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X14">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z14">
-        <v>2.69</v>
+        <v>2.83</v>
       </c>
       <c r="AA14">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="AB14">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="AC14">
-        <v>4.05</v>
+        <v>4.07</v>
       </c>
       <c r="AD14">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AE14">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF14">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="AG14">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK14">
-        <v>1.26</v>
+        <v>2.3</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,80 +2754,80 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.58</v>
+        <v>3.83</v>
       </c>
       <c r="O15">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="P15">
-        <v>5.91</v>
+        <v>1.98</v>
       </c>
       <c r="Q15">
-        <v>2.15</v>
+        <v>4.2</v>
       </c>
       <c r="R15">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S15">
         <v>1.44</v>
       </c>
       <c r="T15">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="U15">
-        <v>3.27</v>
+        <v>3.3</v>
       </c>
       <c r="V15">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W15">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X15">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y15">
+        <v>1.36</v>
+      </c>
+      <c r="Z15">
+        <v>2.69</v>
+      </c>
+      <c r="AA15">
+        <v>2.27</v>
+      </c>
+      <c r="AB15">
+        <v>1.6</v>
+      </c>
+      <c r="AC15">
+        <v>4.05</v>
+      </c>
+      <c r="AD15">
+        <v>1.21</v>
+      </c>
+      <c r="AE15">
+        <v>1.05</v>
+      </c>
+      <c r="AF15">
+        <v>1.95</v>
+      </c>
+      <c r="AG15">
+        <v>1.78</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
         <v>1.33</v>
       </c>
-      <c r="Z15">
-        <v>2.83</v>
-      </c>
-      <c r="AA15">
-        <v>2.15</v>
-      </c>
-      <c r="AB15">
-        <v>1.66</v>
-      </c>
-      <c r="AC15">
-        <v>4.07</v>
-      </c>
-      <c r="AD15">
-        <v>1.23</v>
-      </c>
-      <c r="AE15">
-        <v>1.06</v>
-      </c>
-      <c r="AF15">
-        <v>2.2</v>
-      </c>
-      <c r="AG15">
-        <v>1.65</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.2</v>
-      </c>
       <c r="AK15">
-        <v>2.3</v>
+        <v>1.26</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA16">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB16">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G17">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N17">
@@ -3119,10 +3119,10 @@
         <v>0</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G18">
@@ -3239,68 +3239,68 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T18">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U18">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="V18">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB18">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC18">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK18">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL19">
         <v>0</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="R18">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S18">
         <v>1.4</v>
       </c>
       <c r="T18">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="U18">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="V18">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W18">
+        <v>1.07</v>
+      </c>
+      <c r="X18">
         <v>1.03</v>
       </c>
-      <c r="X18">
-        <v>1</v>
-      </c>
       <c r="Y18">
+        <v>1.34</v>
+      </c>
+      <c r="Z18">
+        <v>2.9</v>
+      </c>
+      <c r="AA18">
+        <v>2.15</v>
+      </c>
+      <c r="AB18">
+        <v>1.73</v>
+      </c>
+      <c r="AC18">
+        <v>3.6</v>
+      </c>
+      <c r="AD18">
         <v>1.23</v>
       </c>
-      <c r="Z18">
-        <v>3.95</v>
-      </c>
-      <c r="AA18">
-        <v>1.98</v>
-      </c>
-      <c r="AB18">
-        <v>1.8</v>
-      </c>
-      <c r="AC18">
-        <v>3</v>
-      </c>
-      <c r="AD18">
-        <v>1.37</v>
-      </c>
       <c r="AE18">
-        <v>1.12</v>
+        <v>1.04</v>
       </c>
       <c r="AF18">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG18">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AK18">
-        <v>2.02</v>
+        <v>1.62</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q19">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="R19">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S19">
         <v>1.4</v>
       </c>
       <c r="T19">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="U19">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="V19">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y19">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="Z19">
-        <v>2.9</v>
+        <v>3.95</v>
       </c>
       <c r="AA19">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AB19">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AC19">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AD19">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="AE19">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AF19">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG19">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AK19">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="AL19">
         <v>0</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
+        <v>2.62</v>
+      </c>
+      <c r="O5">
+        <v>3.4</v>
+      </c>
+      <c r="P5">
+        <v>2.4</v>
+      </c>
+      <c r="Q5">
+        <v>3.3</v>
+      </c>
+      <c r="R5">
+        <v>2.1</v>
+      </c>
+      <c r="S5">
+        <v>1.36</v>
+      </c>
+      <c r="T5">
+        <v>2.89</v>
+      </c>
+      <c r="U5">
         <v>2.73</v>
       </c>
-      <c r="O5">
-        <v>3.39</v>
-      </c>
-      <c r="P5">
-        <v>2.47</v>
-      </c>
-      <c r="Q5">
-        <v>0</v>
-      </c>
-      <c r="R5">
-        <v>0</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
-      </c>
-      <c r="T5">
-        <v>0</v>
-      </c>
-      <c r="U5">
-        <v>0</v>
-      </c>
       <c r="V5">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="W5">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z5">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AA5">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB5">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AD5">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AE5">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF5">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG5">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK5">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>7.95</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>5.19</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z6">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AA6">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC6">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="AD6">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AE6">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AK6">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -2274,55 +2274,55 @@
         <v>3.34</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AL12">
         <v>0</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -2600,55 +2600,55 @@
         <v>5.91</v>
       </c>
       <c r="Q14">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="R14">
         <v>2.1</v>
       </c>
       <c r="S14">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T14">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="U14">
         <v>3.27</v>
       </c>
       <c r="V14">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W14">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y14">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="Z14">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="AA14">
         <v>2.15</v>
       </c>
       <c r="AB14">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="AC14">
-        <v>4.07</v>
+        <v>3.95</v>
       </c>
       <c r="AD14">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE14">
         <v>1.06</v>
       </c>
       <c r="AF14">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AG14">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK14">
         <v>2.3</v>
@@ -2763,55 +2763,55 @@
         <v>1.98</v>
       </c>
       <c r="Q15">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="R15">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="S15">
         <v>1.44</v>
       </c>
       <c r="T15">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="U15">
-        <v>3.3</v>
+        <v>3.16</v>
       </c>
       <c r="V15">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y15">
         <v>1.36</v>
       </c>
       <c r="Z15">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="AA15">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AB15">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC15">
         <v>4.05</v>
       </c>
       <c r="AD15">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AE15">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="AF15">
         <v>1.95</v>
       </c>
       <c r="AG15">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK15">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G17">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N17">
@@ -3089,55 +3089,55 @@
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V17">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W17">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA17">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB17">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="Q18">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="R18">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S18">
         <v>1.4</v>
       </c>
       <c r="T18">
-        <v>2.75</v>
+        <v>2.73</v>
       </c>
       <c r="U18">
-        <v>2.9</v>
+        <v>2.63</v>
       </c>
       <c r="V18">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="W18">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X18">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y18">
-        <v>1.34</v>
+        <v>1.23</v>
       </c>
       <c r="Z18">
-        <v>2.9</v>
+        <v>3.95</v>
       </c>
       <c r="AA18">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AB18">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="AC18">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AD18">
-        <v>1.23</v>
+        <v>1.37</v>
       </c>
       <c r="AE18">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AF18">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG18">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AK18">
-        <v>1.62</v>
+        <v>2.02</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G19">
@@ -3402,68 +3402,68 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N19">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="R19">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="S19">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T19">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="U19">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="V19">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W19">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="Z19">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="AA19">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="AB19">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC19">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD19">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AE19">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AF19">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AG19">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK19">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AL19">
         <v>0</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -1124,61 +1124,61 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.62</v>
+        <v>2.82</v>
       </c>
       <c r="O5">
         <v>3.4</v>
       </c>
       <c r="P5">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q5">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R5">
         <v>2.1</v>
       </c>
       <c r="S5">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="T5">
         <v>2.89</v>
       </c>
       <c r="U5">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="V5">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="W5">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X5">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="Z5">
-        <v>3.38</v>
+        <v>3.55</v>
       </c>
       <c r="AA5">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AB5">
         <v>1.85</v>
       </c>
       <c r="AC5">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="AD5">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AE5">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="AF5">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AG5">
         <v>2.05</v>
@@ -1197,7 +1197,7 @@
         <v>1.29</v>
       </c>
       <c r="AK5">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>7.95</v>
+        <v>5.65</v>
       </c>
       <c r="O6">
-        <v>5.19</v>
+        <v>5.3</v>
       </c>
       <c r="P6">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="Q6">
-        <v>6.85</v>
+        <v>6</v>
       </c>
       <c r="R6">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="S6">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T6">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="U6">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="V6">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W6">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
         <v>1.01</v>
       </c>
       <c r="Y6">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z6">
-        <v>3.88</v>
+        <v>4.1</v>
       </c>
       <c r="AA6">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB6">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AC6">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="AD6">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE6">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AF6">
         <v>1.97</v>
       </c>
       <c r="AG6">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AK6">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.19</v>
+        <v>2.58</v>
       </c>
       <c r="O7">
-        <v>3.55</v>
+        <v>3.42</v>
       </c>
       <c r="P7">
-        <v>2.09</v>
+        <v>2.55</v>
       </c>
       <c r="Q7">
-        <v>3.31</v>
+        <v>2.54</v>
       </c>
       <c r="R7">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="S7">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="T7">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="U7">
-        <v>2.5</v>
+        <v>2.41</v>
       </c>
       <c r="V7">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W7">
         <v>1.08</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y7">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z7">
-        <v>3.9</v>
+        <v>4.25</v>
       </c>
       <c r="AA7">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AB7">
-        <v>2.04</v>
+        <v>2.19</v>
       </c>
       <c r="AC7">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="AD7">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="AE7">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="AF7">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AG7">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.25</v>
       </c>
       <c r="AK7">
-        <v>1.31</v>
+        <v>1.53</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.58</v>
+        <v>3.15</v>
       </c>
       <c r="O8">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="P8">
-        <v>2.55</v>
+        <v>2.06</v>
       </c>
       <c r="Q8">
-        <v>2.54</v>
+        <v>3.45</v>
       </c>
       <c r="R8">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S8">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T8">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U8">
-        <v>2.41</v>
+        <v>2.28</v>
       </c>
       <c r="V8">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W8">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y8">
         <v>1.2</v>
       </c>
       <c r="Z8">
-        <v>4.3</v>
+        <v>4.27</v>
       </c>
       <c r="AA8">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="AB8">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="AC8">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="AD8">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="AE8">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AF8">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AG8">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK8">
-        <v>1.53</v>
+        <v>1.31</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="O9">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="P9">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="Q9">
         <v>1.85</v>
       </c>
       <c r="R9">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="S9">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="T9">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="U9">
-        <v>2.43</v>
+        <v>2.29</v>
       </c>
       <c r="V9">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="W9">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z9">
-        <v>3.82</v>
+        <v>4.4</v>
       </c>
       <c r="AA9">
-        <v>1.71</v>
+        <v>1.66</v>
       </c>
       <c r="AB9">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AC9">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="AD9">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="AE9">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AF9">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AG9">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AK9">
-        <v>2.85</v>
+        <v>2.7</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="O11">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="P11">
-        <v>8</v>
+        <v>6.45</v>
       </c>
       <c r="Q11">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="R11">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="S11">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T11">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="U11">
-        <v>2.53</v>
+        <v>2.29</v>
       </c>
       <c r="V11">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="W11">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="X11">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="Z11">
-        <v>3.82</v>
+        <v>4.1</v>
       </c>
       <c r="AA11">
-        <v>1.78</v>
+        <v>1.67</v>
       </c>
       <c r="AB11">
-        <v>1.9</v>
+        <v>2.16</v>
       </c>
       <c r="AC11">
-        <v>2.9</v>
+        <v>2.51</v>
       </c>
       <c r="AD11">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AE11">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AF11">
-        <v>2.06</v>
+        <v>1.83</v>
       </c>
       <c r="AG11">
-        <v>1.68</v>
+        <v>1.79</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK11">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,43 +2265,43 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.96</v>
+        <v>1.76</v>
       </c>
       <c r="O12">
         <v>3.9</v>
       </c>
       <c r="P12">
-        <v>3.34</v>
+        <v>4</v>
       </c>
       <c r="Q12">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="R12">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="S12">
         <v>1.25</v>
       </c>
       <c r="T12">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="U12">
         <v>2.27</v>
       </c>
       <c r="V12">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W12">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X12">
         <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="Z12">
-        <v>4.55</v>
+        <v>4.75</v>
       </c>
       <c r="AA12">
         <v>1.57</v>
@@ -2310,19 +2310,19 @@
         <v>2.35</v>
       </c>
       <c r="AC12">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="AD12">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE12">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AF12">
         <v>1.52</v>
       </c>
       <c r="AG12">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.23</v>
       </c>
       <c r="AK12">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,64 +2428,64 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="O13">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="P13">
         <v>4</v>
       </c>
       <c r="Q13">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="R13">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="S13">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T13">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="U13">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="V13">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W13">
         <v>1.11</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y13">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>3.62</v>
+        <v>4</v>
       </c>
       <c r="AA13">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AB13">
-        <v>2.01</v>
+        <v>1.92</v>
       </c>
       <c r="AC13">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="AD13">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE13">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="AF13">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="AG13">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AK13">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2618,10 +2618,10 @@
         <v>1.29</v>
       </c>
       <c r="W14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X14">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
         <v>1.4</v>
@@ -2633,13 +2633,13 @@
         <v>2.15</v>
       </c>
       <c r="AB14">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AC14">
-        <v>3.95</v>
+        <v>4.34</v>
       </c>
       <c r="AD14">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AE14">
         <v>1.06</v>
@@ -2778,10 +2778,10 @@
         <v>3.16</v>
       </c>
       <c r="V15">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W15">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="X15">
         <v>1.03</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="N16">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="O16">
         <v>3.3</v>
@@ -2926,16 +2926,16 @@
         <v>3.75</v>
       </c>
       <c r="Q16">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="R16">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="S16">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T16">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="U16">
         <v>2.9</v>
@@ -2944,19 +2944,19 @@
         <v>1.34</v>
       </c>
       <c r="W16">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X16">
         <v>1.03</v>
       </c>
       <c r="Y16">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z16">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AA16">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AB16">
         <v>1.66</v>
@@ -3095,13 +3095,13 @@
         <v>2.1</v>
       </c>
       <c r="S17">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T17">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="U17">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V17">
         <v>1.36</v>
@@ -3243,19 +3243,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="O18">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="P18">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="R18">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S18">
         <v>1.4</v>
@@ -3264,28 +3264,28 @@
         <v>2.73</v>
       </c>
       <c r="U18">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="V18">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W18">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y18">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="Z18">
-        <v>3.95</v>
+        <v>3.25</v>
       </c>
       <c r="AA18">
         <v>1.98</v>
       </c>
       <c r="AB18">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AC18">
         <v>3</v>
@@ -3294,7 +3294,7 @@
         <v>1.37</v>
       </c>
       <c r="AE18">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
       <c r="AF18">
         <v>1.87</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK18">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="O20">
-        <v>3.48</v>
+        <v>3.35</v>
       </c>
       <c r="P20">
-        <v>4.88</v>
+        <v>5.2</v>
       </c>
       <c r="Q20">
         <v>0</v>
@@ -3608,10 +3608,10 @@
         <v>0</v>
       </c>
       <c r="AA20">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AB20">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AC20">
         <v>0</v>
@@ -3732,64 +3732,64 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="O21">
-        <v>4.65</v>
+        <v>4.85</v>
       </c>
       <c r="P21">
-        <v>6.5</v>
+        <v>9.35</v>
       </c>
       <c r="Q21">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="R21">
-        <v>2.3</v>
+        <v>2.55</v>
       </c>
       <c r="S21">
         <v>1.25</v>
       </c>
       <c r="T21">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="U21">
-        <v>2.48</v>
+        <v>2.25</v>
       </c>
       <c r="V21">
+        <v>1.62</v>
+      </c>
+      <c r="W21">
+        <v>1.17</v>
+      </c>
+      <c r="X21">
+        <v>1.04</v>
+      </c>
+      <c r="Y21">
+        <v>1.18</v>
+      </c>
+      <c r="Z21">
+        <v>4.5</v>
+      </c>
+      <c r="AA21">
+        <v>1.73</v>
+      </c>
+      <c r="AB21">
+        <v>2.38</v>
+      </c>
+      <c r="AC21">
+        <v>2.35</v>
+      </c>
+      <c r="AD21">
         <v>1.5</v>
-      </c>
-      <c r="W21">
-        <v>1.1</v>
-      </c>
-      <c r="X21">
-        <v>1.02</v>
-      </c>
-      <c r="Y21">
-        <v>1.17</v>
-      </c>
-      <c r="Z21">
-        <v>4</v>
-      </c>
-      <c r="AA21">
-        <v>1.66</v>
-      </c>
-      <c r="AB21">
-        <v>2.1</v>
-      </c>
-      <c r="AC21">
-        <v>2.56</v>
-      </c>
-      <c r="AD21">
-        <v>1.43</v>
       </c>
       <c r="AE21">
         <v>1.13</v>
       </c>
       <c r="AF21">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AG21">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>1.12</v>
       </c>
       <c r="AK21">
-        <v>2.88</v>
+        <v>2.43</v>
       </c>
       <c r="AL21">
         <v>0</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -2618,7 +2618,7 @@
         <v>1.29</v>
       </c>
       <c r="W14">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X14">
         <v>1.03</v>
@@ -2763,13 +2763,13 @@
         <v>1.98</v>
       </c>
       <c r="Q15">
-        <v>4.4</v>
+        <v>4.57</v>
       </c>
       <c r="R15">
         <v>1.97</v>
       </c>
       <c r="S15">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="T15">
         <v>2.62</v>
@@ -2778,7 +2778,7 @@
         <v>3.16</v>
       </c>
       <c r="V15">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W15">
         <v>1.02</v>
@@ -2808,10 +2808,10 @@
         <v>1.02</v>
       </c>
       <c r="AF15">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AG15">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AK15">
         <v>1.25</v>
@@ -3572,10 +3572,10 @@
         <v>1.71</v>
       </c>
       <c r="O20">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="P20">
-        <v>5.2</v>
+        <v>4.33</v>
       </c>
       <c r="Q20">
         <v>0</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G16">
@@ -2913,68 +2913,68 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N16">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q16">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="R16">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="AB16">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC16">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,31 +3080,31 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="Q17">
+        <v>2.62</v>
+      </c>
+      <c r="R17">
+        <v>2.05</v>
+      </c>
+      <c r="S17">
+        <v>1.4</v>
+      </c>
+      <c r="T17">
         <v>2.7</v>
       </c>
-      <c r="R17">
-        <v>2.1</v>
-      </c>
-      <c r="S17">
-        <v>1.42</v>
-      </c>
-      <c r="T17">
-        <v>2.65</v>
-      </c>
       <c r="U17">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V17">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W17">
         <v>1.07</v>
@@ -3113,31 +3113,31 @@
         <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z17">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AA17">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AB17">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AC17">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AD17">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE17">
         <v>1.04</v>
       </c>
       <c r="AF17">
-        <v>1.85</v>
+        <v>1.92</v>
       </c>
       <c r="AG17">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="AK17">
-        <v>1.62</v>
+        <v>1.79</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="P18">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q18">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="R18">
         <v>2.1</v>
       </c>
       <c r="S18">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T18">
-        <v>2.73</v>
+        <v>2.65</v>
       </c>
       <c r="U18">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V18">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X18">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z18">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="AA18">
-        <v>1.98</v>
+        <v>2.15</v>
       </c>
       <c r="AB18">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="AC18">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="AD18">
-        <v>1.37</v>
+        <v>1.23</v>
       </c>
       <c r="AE18">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF18">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG18">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AK18">
-        <v>2.12</v>
+        <v>1.62</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G19">
@@ -3402,68 +3402,68 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T19">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA19">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AB19">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AL19">
         <v>0</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -1459,16 +1459,16 @@
         <v>2.55</v>
       </c>
       <c r="Q7">
-        <v>2.54</v>
+        <v>2.88</v>
       </c>
       <c r="R7">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="S7">
         <v>1.25</v>
       </c>
       <c r="T7">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="U7">
         <v>2.41</v>
@@ -1489,13 +1489,13 @@
         <v>4.25</v>
       </c>
       <c r="AA7">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AB7">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AC7">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="AD7">
         <v>1.49</v>
@@ -1504,10 +1504,10 @@
         <v>1.19</v>
       </c>
       <c r="AF7">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG7">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AK7">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,19 +1613,19 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="O8">
         <v>3.5</v>
       </c>
       <c r="P8">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="Q8">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="R8">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S8">
         <v>1.3</v>
@@ -1649,16 +1649,16 @@
         <v>1.2</v>
       </c>
       <c r="Z8">
-        <v>4.27</v>
+        <v>4.28</v>
       </c>
       <c r="AA8">
         <v>1.68</v>
       </c>
       <c r="AB8">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AC8">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AD8">
         <v>1.47</v>
@@ -1670,7 +1670,7 @@
         <v>1.56</v>
       </c>
       <c r="AG8">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AK8">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AL8">
         <v>0</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="O5">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="P5">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="Q5">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="R5">
         <v>2.1</v>
@@ -1145,43 +1145,43 @@
         <v>2.89</v>
       </c>
       <c r="U5">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="V5">
         <v>1.4</v>
       </c>
       <c r="W5">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
         <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z5">
-        <v>3.55</v>
+        <v>3.1</v>
       </c>
       <c r="AA5">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AB5">
         <v>1.85</v>
       </c>
       <c r="AC5">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="AD5">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AE5">
         <v>1.07</v>
       </c>
       <c r="AF5">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AG5">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="AK5">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,64 +1287,64 @@
         </is>
       </c>
       <c r="N6">
-        <v>5.65</v>
+        <v>4.8</v>
       </c>
       <c r="O6">
-        <v>5.3</v>
+        <v>4.75</v>
       </c>
       <c r="P6">
-        <v>1.38</v>
+        <v>1.49</v>
       </c>
       <c r="Q6">
-        <v>6</v>
+        <v>5.75</v>
       </c>
       <c r="R6">
         <v>2.45</v>
       </c>
       <c r="S6">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T6">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="U6">
         <v>2.4</v>
       </c>
       <c r="V6">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z6">
         <v>4.1</v>
       </c>
       <c r="AA6">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="AB6">
-        <v>2.14</v>
+        <v>1.99</v>
       </c>
       <c r="AC6">
-        <v>2.5</v>
+        <v>2.76</v>
       </c>
       <c r="AD6">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AE6">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AF6">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="AG6">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AK6">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1489,10 +1489,10 @@
         <v>4.25</v>
       </c>
       <c r="AA7">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB7">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC7">
         <v>2.46</v>
@@ -1652,7 +1652,7 @@
         <v>4.28</v>
       </c>
       <c r="AA8">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB8">
         <v>2.05</v>
@@ -1776,49 +1776,49 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="O9">
-        <v>5</v>
+        <v>5.25</v>
       </c>
       <c r="P9">
-        <v>8</v>
+        <v>7.5</v>
       </c>
       <c r="Q9">
         <v>1.85</v>
       </c>
       <c r="R9">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="S9">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="T9">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="U9">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="V9">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="W9">
         <v>1.11</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y9">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Z9">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA9">
         <v>1.66</v>
       </c>
       <c r="AB9">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="AC9">
         <v>2.55</v>
@@ -1830,10 +1830,10 @@
         <v>1.14</v>
       </c>
       <c r="AF9">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AG9">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.16</v>
+        <v>1.11</v>
       </c>
       <c r="AK9">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="O11">
-        <v>4.8</v>
+        <v>4.83</v>
       </c>
       <c r="P11">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="Q11">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="R11">
-        <v>2.52</v>
+        <v>2.59</v>
       </c>
       <c r="S11">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T11">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="U11">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="V11">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="W11">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="Z11">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="AA11">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AB11">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="AC11">
-        <v>2.51</v>
+        <v>2.42</v>
       </c>
       <c r="AD11">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AE11">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF11">
         <v>1.83</v>
       </c>
       <c r="AG11">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="AK11">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,37 +2265,37 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="O12">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="P12">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="Q12">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="R12">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="S12">
         <v>1.25</v>
       </c>
       <c r="T12">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="U12">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="V12">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W12">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
         <v>1.15</v>
@@ -2307,22 +2307,22 @@
         <v>1.57</v>
       </c>
       <c r="AB12">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="AC12">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="AD12">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE12">
         <v>1.18</v>
       </c>
       <c r="AF12">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG12">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AK12">
         <v>1.95</v>
@@ -2431,10 +2431,10 @@
         <v>1.82</v>
       </c>
       <c r="O13">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="P13">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q13">
         <v>2.38</v>
@@ -2464,28 +2464,28 @@
         <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AA13">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AB13">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="AC13">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="AD13">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="AE13">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AF13">
         <v>1.67</v>
       </c>
       <c r="AG13">
-        <v>2.09</v>
+        <v>1.98</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1.25</v>
       </c>
       <c r="AK13">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2606,46 +2606,46 @@
         <v>2.1</v>
       </c>
       <c r="S14">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="T14">
         <v>2.42</v>
       </c>
       <c r="U14">
-        <v>3.27</v>
+        <v>3.22</v>
       </c>
       <c r="V14">
         <v>1.29</v>
       </c>
       <c r="W14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z14">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="AA14">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB14">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC14">
         <v>4.34</v>
       </c>
       <c r="AD14">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="AE14">
         <v>1.06</v>
       </c>
       <c r="AF14">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AG14">
         <v>1.57</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
       <c r="AK14">
         <v>2.3</v>
@@ -2763,22 +2763,22 @@
         <v>1.98</v>
       </c>
       <c r="Q15">
-        <v>4.57</v>
+        <v>3.9</v>
       </c>
       <c r="R15">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="S15">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="T15">
         <v>2.62</v>
       </c>
       <c r="U15">
-        <v>3.16</v>
+        <v>3.1</v>
       </c>
       <c r="V15">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="W15">
         <v>1.02</v>
@@ -2808,10 +2808,10 @@
         <v>1.02</v>
       </c>
       <c r="AF15">
-        <v>1.9</v>
+        <v>1.93</v>
       </c>
       <c r="AG15">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK15">
         <v>1.25</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q17">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="R17">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S17">
         <v>1.4</v>
       </c>
       <c r="T17">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="U17">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="V17">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W17">
         <v>1.07</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y17">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z17">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="AA17">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="AB17">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AC17">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AD17">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE17">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF17">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AG17">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AK17">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>2.7</v>
+        <v>2.28</v>
       </c>
       <c r="R18">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="S18">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="T18">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="U18">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V18">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="W18">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y18">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="Z18">
-        <v>2.9</v>
+        <v>3.18</v>
       </c>
       <c r="AA18">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AB18">
-        <v>1.73</v>
+        <v>1.97</v>
       </c>
       <c r="AC18">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="AD18">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE18">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF18">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AG18">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="AK18">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,80 +3406,80 @@
         </is>
       </c>
       <c r="N19">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="O19">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P19">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="Q19">
-        <v>2.25</v>
+        <v>2.62</v>
       </c>
       <c r="R19">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S19">
         <v>1.4</v>
       </c>
       <c r="T19">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="U19">
-        <v>2.75</v>
+        <v>3.04</v>
       </c>
       <c r="V19">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W19">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y19">
+        <v>1.38</v>
+      </c>
+      <c r="Z19">
+        <v>2.8</v>
+      </c>
+      <c r="AA19">
+        <v>2.15</v>
+      </c>
+      <c r="AB19">
+        <v>1.66</v>
+      </c>
+      <c r="AC19">
+        <v>3.85</v>
+      </c>
+      <c r="AD19">
+        <v>1.22</v>
+      </c>
+      <c r="AE19">
+        <v>1.07</v>
+      </c>
+      <c r="AF19">
+        <v>1.85</v>
+      </c>
+      <c r="AG19">
+        <v>1.91</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ19">
         <v>1.33</v>
       </c>
-      <c r="Z19">
-        <v>3.25</v>
-      </c>
-      <c r="AA19">
-        <v>1.98</v>
-      </c>
-      <c r="AB19">
-        <v>1.98</v>
-      </c>
-      <c r="AC19">
-        <v>3</v>
-      </c>
-      <c r="AD19">
-        <v>1.37</v>
-      </c>
-      <c r="AE19">
-        <v>1.05</v>
-      </c>
-      <c r="AF19">
-        <v>1.87</v>
-      </c>
-      <c r="AG19">
-        <v>1.83</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ19">
-        <v>1.22</v>
-      </c>
       <c r="AK19">
-        <v>2.12</v>
+        <v>1.75</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         <v>1.28</v>
       </c>
       <c r="O21">
-        <v>4.85</v>
+        <v>4.75</v>
       </c>
       <c r="P21">
-        <v>9.35</v>
+        <v>7.9</v>
       </c>
       <c r="Q21">
         <v>1.91</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -3101,7 +3101,7 @@
         <v>2.75</v>
       </c>
       <c r="U17">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="V17">
         <v>1.36</v>
@@ -3110,10 +3110,10 @@
         <v>1.07</v>
       </c>
       <c r="X17">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="Z17">
         <v>3.1</v>
@@ -3122,13 +3122,13 @@
         <v>2.04</v>
       </c>
       <c r="AB17">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC17">
         <v>3.6</v>
       </c>
       <c r="AD17">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE17">
         <v>1.07</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O18">
         <v>3.5</v>
@@ -3258,31 +3258,31 @@
         <v>2.07</v>
       </c>
       <c r="S18">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="T18">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="U18">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="V18">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X18">
         <v>1.06</v>
       </c>
       <c r="Y18">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z18">
         <v>3.18</v>
       </c>
       <c r="AA18">
-        <v>1.98</v>
+        <v>1.92</v>
       </c>
       <c r="AB18">
         <v>1.97</v>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AK18">
         <v>2.05</v>
@@ -3418,25 +3418,25 @@
         <v>2.62</v>
       </c>
       <c r="R19">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S19">
         <v>1.4</v>
       </c>
       <c r="T19">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="U19">
         <v>3.04</v>
       </c>
       <c r="V19">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W19">
         <v>1.07</v>
       </c>
       <c r="X19">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
         <v>1.38</v>
@@ -3451,10 +3451,10 @@
         <v>1.66</v>
       </c>
       <c r="AC19">
-        <v>3.85</v>
+        <v>3.62</v>
       </c>
       <c r="AD19">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="AE19">
         <v>1.07</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="O21">
         <v>4.75</v>
       </c>
       <c r="P21">
-        <v>7.9</v>
+        <v>6.84</v>
       </c>
       <c r="Q21">
         <v>1.91</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -1124,49 +1124,49 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O5">
         <v>3.2</v>
       </c>
       <c r="P5">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="Q5">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="R5">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S5">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="T5">
-        <v>2.89</v>
+        <v>2.7</v>
       </c>
       <c r="U5">
-        <v>2.62</v>
+        <v>2.55</v>
       </c>
       <c r="V5">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W5">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
         <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z5">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AA5">
         <v>1.94</v>
       </c>
       <c r="AB5">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AC5">
         <v>3.05</v>
@@ -1175,13 +1175,13 @@
         <v>1.31</v>
       </c>
       <c r="AE5">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF5">
         <v>1.7</v>
       </c>
       <c r="AG5">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AK5">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,10 +1287,10 @@
         </is>
       </c>
       <c r="N6">
-        <v>4.8</v>
+        <v>6.5</v>
       </c>
       <c r="O6">
-        <v>4.75</v>
+        <v>4.1</v>
       </c>
       <c r="P6">
         <v>1.49</v>
@@ -1308,43 +1308,43 @@
         <v>3.25</v>
       </c>
       <c r="U6">
-        <v>2.4</v>
+        <v>2.54</v>
       </c>
       <c r="V6">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
         <v>1.2</v>
       </c>
       <c r="Z6">
-        <v>4.1</v>
+        <v>3.74</v>
       </c>
       <c r="AA6">
-        <v>1.76</v>
+        <v>1.63</v>
       </c>
       <c r="AB6">
-        <v>1.99</v>
+        <v>2.08</v>
       </c>
       <c r="AC6">
-        <v>2.76</v>
+        <v>2.6</v>
       </c>
       <c r="AD6">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="AE6">
         <v>1.1</v>
       </c>
       <c r="AF6">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AG6">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AK6">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1459,16 +1459,16 @@
         <v>2.55</v>
       </c>
       <c r="Q7">
-        <v>2.88</v>
+        <v>2.54</v>
       </c>
       <c r="R7">
-        <v>2.13</v>
+        <v>2.3</v>
       </c>
       <c r="S7">
         <v>1.25</v>
       </c>
       <c r="T7">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="U7">
         <v>2.41</v>
@@ -1477,7 +1477,7 @@
         <v>1.49</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X7">
         <v>1.04</v>
@@ -1489,10 +1489,10 @@
         <v>4.25</v>
       </c>
       <c r="AA7">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AB7">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC7">
         <v>2.46</v>
@@ -1501,13 +1501,13 @@
         <v>1.49</v>
       </c>
       <c r="AE7">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AF7">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AG7">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1622,7 +1622,7 @@
         <v>1.97</v>
       </c>
       <c r="Q8">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="R8">
         <v>2.38</v>
@@ -1637,7 +1637,7 @@
         <v>2.28</v>
       </c>
       <c r="V8">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="W8">
         <v>1.12</v>
@@ -1655,7 +1655,7 @@
         <v>1.67</v>
       </c>
       <c r="AB8">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AC8">
         <v>2.52</v>
@@ -1776,37 +1776,37 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="O9">
-        <v>5.25</v>
+        <v>4.8</v>
       </c>
       <c r="P9">
-        <v>7.5</v>
+        <v>7.75</v>
       </c>
       <c r="Q9">
         <v>1.85</v>
       </c>
       <c r="R9">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="S9">
         <v>1.25</v>
       </c>
       <c r="T9">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U9">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="V9">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X9">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y9">
         <v>1.2</v>
@@ -1815,25 +1815,25 @@
         <v>4.33</v>
       </c>
       <c r="AA9">
-        <v>1.66</v>
+        <v>1.6</v>
       </c>
       <c r="AB9">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="AC9">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="AD9">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AE9">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AF9">
         <v>1.85</v>
       </c>
       <c r="AG9">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AK9">
-        <v>2.82</v>
+        <v>2.99</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>5.73</v>
       </c>
       <c r="Q10">
         <v>1.97</v>
@@ -2102,25 +2102,25 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="O11">
         <v>4.83</v>
       </c>
       <c r="P11">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="Q11">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="R11">
-        <v>2.59</v>
+        <v>2.42</v>
       </c>
       <c r="S11">
         <v>1.3</v>
       </c>
       <c r="T11">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U11">
         <v>2.27</v>
@@ -2135,13 +2135,13 @@
         <v>1.04</v>
       </c>
       <c r="Y11">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z11">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AA11">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AB11">
         <v>2.26</v>
@@ -2156,7 +2156,7 @@
         <v>1.14</v>
       </c>
       <c r="AF11">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AG11">
         <v>1.81</v>
@@ -2265,40 +2265,40 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="O12">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="P12">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="Q12">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="R12">
-        <v>2.47</v>
+        <v>2.28</v>
       </c>
       <c r="S12">
         <v>1.25</v>
       </c>
       <c r="T12">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="U12">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="V12">
         <v>1.59</v>
       </c>
       <c r="W12">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y12">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z12">
         <v>4.75</v>
@@ -2307,16 +2307,16 @@
         <v>1.57</v>
       </c>
       <c r="AB12">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AC12">
         <v>2.31</v>
       </c>
       <c r="AD12">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="AE12">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF12">
         <v>1.5</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="AK12">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,10 +2428,10 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="O13">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P13">
         <v>3.9</v>
@@ -2449,10 +2449,10 @@
         <v>3.25</v>
       </c>
       <c r="U13">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="V13">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W13">
         <v>1.11</v>
@@ -2464,28 +2464,28 @@
         <v>1.22</v>
       </c>
       <c r="Z13">
-        <v>4.2</v>
+        <v>3.74</v>
       </c>
       <c r="AA13">
-        <v>1.65</v>
+        <v>1.74</v>
       </c>
       <c r="AB13">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AC13">
-        <v>2.9</v>
+        <v>2.71</v>
       </c>
       <c r="AD13">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="AE13">
         <v>1.11</v>
       </c>
       <c r="AF13">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="AG13">
-        <v>1.98</v>
+        <v>2.09</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2501,7 +2501,7 @@
         <v>1.25</v>
       </c>
       <c r="AK13">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2609,43 +2609,43 @@
         <v>1.41</v>
       </c>
       <c r="T14">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="U14">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="V14">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W14">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
         <v>1.42</v>
       </c>
       <c r="Z14">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="AA14">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB14">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AC14">
-        <v>4.34</v>
+        <v>4.4</v>
       </c>
       <c r="AD14">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE14">
         <v>1.06</v>
       </c>
       <c r="AF14">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AG14">
         <v>1.57</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.12</v>
+        <v>1.26</v>
       </c>
       <c r="AK14">
         <v>2.3</v>
@@ -2763,28 +2763,28 @@
         <v>1.98</v>
       </c>
       <c r="Q15">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="R15">
         <v>2.05</v>
       </c>
       <c r="S15">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="T15">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="U15">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="V15">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="W15">
         <v>1.02</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
         <v>1.36</v>
@@ -2796,22 +2796,22 @@
         <v>2.25</v>
       </c>
       <c r="AB15">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AC15">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="AD15">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AE15">
         <v>1.02</v>
       </c>
       <c r="AF15">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG15">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.26</v>
+        <v>1.61</v>
       </c>
       <c r="AK15">
         <v>1.25</v>
@@ -3095,31 +3095,31 @@
         <v>2.1</v>
       </c>
       <c r="S17">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="T17">
         <v>2.75</v>
       </c>
       <c r="U17">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="V17">
         <v>1.36</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y17">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Z17">
         <v>3.1</v>
       </c>
       <c r="AA17">
-        <v>2.04</v>
+        <v>2.15</v>
       </c>
       <c r="AB17">
         <v>1.73</v>
@@ -3128,7 +3128,7 @@
         <v>3.6</v>
       </c>
       <c r="AD17">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AE17">
         <v>1.07</v>
@@ -3150,7 +3150,7 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AK17">
         <v>1.69</v>
@@ -3258,34 +3258,34 @@
         <v>2.07</v>
       </c>
       <c r="S18">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="T18">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="U18">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="V18">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="W18">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
         <v>1.06</v>
       </c>
       <c r="Y18">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="Z18">
         <v>3.18</v>
       </c>
       <c r="AA18">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="AB18">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AC18">
         <v>3.05</v>
@@ -3421,7 +3421,7 @@
         <v>2.1</v>
       </c>
       <c r="S19">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T19">
         <v>2.62</v>
@@ -3433,7 +3433,7 @@
         <v>1.35</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X19">
         <v>1.03</v>
@@ -3445,10 +3445,10 @@
         <v>2.8</v>
       </c>
       <c r="AA19">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="AB19">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="AC19">
         <v>3.62</v>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
         <v>1.75</v>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="O20">
         <v>3.3</v>
@@ -3732,7 +3732,7 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="O21">
         <v>4.75</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -1468,7 +1468,7 @@
         <v>1.25</v>
       </c>
       <c r="T7">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="U7">
         <v>2.41</v>
@@ -1631,7 +1631,7 @@
         <v>1.3</v>
       </c>
       <c r="T8">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U8">
         <v>2.28</v>
@@ -1652,10 +1652,10 @@
         <v>4.28</v>
       </c>
       <c r="AA8">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AB8">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AC8">
         <v>2.52</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -1489,10 +1489,10 @@
         <v>4.25</v>
       </c>
       <c r="AA7">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AB7">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC7">
         <v>2.46</v>
@@ -1501,7 +1501,7 @@
         <v>1.49</v>
       </c>
       <c r="AE7">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF7">
         <v>1.51</v>
@@ -2606,7 +2606,7 @@
         <v>2.1</v>
       </c>
       <c r="S14">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="T14">
         <v>2.41</v>
@@ -2627,7 +2627,7 @@
         <v>1.42</v>
       </c>
       <c r="Z14">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
       <c r="AA14">
         <v>2.25</v>
@@ -2642,7 +2642,7 @@
         <v>1.18</v>
       </c>
       <c r="AE14">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF14">
         <v>2.15</v>
@@ -2664,7 +2664,7 @@
         <v>1.26</v>
       </c>
       <c r="AK14">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2763,7 +2763,7 @@
         <v>1.98</v>
       </c>
       <c r="Q15">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="R15">
         <v>2.05</v>
@@ -2790,13 +2790,13 @@
         <v>1.36</v>
       </c>
       <c r="Z15">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="AA15">
         <v>2.25</v>
       </c>
       <c r="AB15">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC15">
         <v>3.95</v>
@@ -2808,7 +2808,7 @@
         <v>1.02</v>
       </c>
       <c r="AF15">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AG15">
         <v>1.77</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="AK15">
         <v>1.25</v>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="O20">
         <v>3.3</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -1124,13 +1124,13 @@
         </is>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="O5">
         <v>3.2</v>
       </c>
       <c r="P5">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q5">
         <v>3.4</v>
@@ -1142,7 +1142,7 @@
         <v>1.36</v>
       </c>
       <c r="T5">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="U5">
         <v>2.55</v>
@@ -1151,7 +1151,7 @@
         <v>1.43</v>
       </c>
       <c r="W5">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
         <v>1.03</v>
@@ -1160,13 +1160,13 @@
         <v>1.24</v>
       </c>
       <c r="Z5">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AA5">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB5">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AC5">
         <v>3.05</v>
@@ -1175,10 +1175,10 @@
         <v>1.31</v>
       </c>
       <c r="AE5">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="AF5">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AG5">
         <v>2</v>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AK5">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1290,16 +1290,16 @@
         <v>6.5</v>
       </c>
       <c r="O6">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="P6">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="Q6">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="R6">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="S6">
         <v>1.29</v>
@@ -1308,43 +1308,43 @@
         <v>3.25</v>
       </c>
       <c r="U6">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="V6">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y6">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z6">
-        <v>3.74</v>
+        <v>3.62</v>
       </c>
       <c r="AA6">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AB6">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="AC6">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="AD6">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AE6">
         <v>1.1</v>
       </c>
       <c r="AF6">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AG6">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AK6">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1776,19 +1776,19 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="O9">
-        <v>4.8</v>
+        <v>5.25</v>
       </c>
       <c r="P9">
-        <v>7.75</v>
+        <v>7.5</v>
       </c>
       <c r="Q9">
         <v>1.85</v>
       </c>
       <c r="R9">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="S9">
         <v>1.25</v>
@@ -1797,10 +1797,10 @@
         <v>3.15</v>
       </c>
       <c r="U9">
-        <v>2.31</v>
+        <v>2.25</v>
       </c>
       <c r="V9">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="W9">
         <v>1.13</v>
@@ -1815,25 +1815,25 @@
         <v>4.33</v>
       </c>
       <c r="AA9">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB9">
         <v>2.2</v>
       </c>
       <c r="AC9">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="AD9">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AE9">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AF9">
         <v>1.85</v>
       </c>
       <c r="AG9">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -2102,7 +2102,7 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="O11">
         <v>4.83</v>
@@ -2117,10 +2117,10 @@
         <v>2.42</v>
       </c>
       <c r="S11">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T11">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="U11">
         <v>2.27</v>
@@ -2132,13 +2132,13 @@
         <v>1.11</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
         <v>1.2</v>
       </c>
       <c r="Z11">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA11">
         <v>1.62</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AK11">
         <v>2.88</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="O12">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="P12">
         <v>4</v>
@@ -2289,10 +2289,10 @@
         <v>2.22</v>
       </c>
       <c r="V12">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="W12">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X12">
         <v>1.02</v>
@@ -2301,10 +2301,10 @@
         <v>1.13</v>
       </c>
       <c r="Z12">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AA12">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="AB12">
         <v>2.35</v>
@@ -2313,7 +2313,7 @@
         <v>2.31</v>
       </c>
       <c r="AD12">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE12">
         <v>1.17</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AK12">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="O13">
         <v>3.6</v>
@@ -2437,7 +2437,7 @@
         <v>3.9</v>
       </c>
       <c r="Q13">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="R13">
         <v>2.25</v>
@@ -2458,19 +2458,19 @@
         <v>1.11</v>
       </c>
       <c r="X13">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="Z13">
         <v>3.74</v>
       </c>
       <c r="AA13">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AB13">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="AC13">
         <v>2.71</v>
@@ -2479,7 +2479,7 @@
         <v>1.41</v>
       </c>
       <c r="AE13">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="AF13">
         <v>1.66</v>
@@ -2956,10 +2956,10 @@
         <v>0</v>
       </c>
       <c r="AA16">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB16">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC16">
         <v>0</v>
@@ -3089,7 +3089,7 @@
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R17">
         <v>2.1</v>
@@ -3113,16 +3113,16 @@
         <v>1.06</v>
       </c>
       <c r="Y17">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z17">
         <v>3.1</v>
       </c>
       <c r="AA17">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="AB17">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AC17">
         <v>3.6</v>
@@ -3252,22 +3252,22 @@
         <v>5</v>
       </c>
       <c r="Q18">
-        <v>2.28</v>
+        <v>2.25</v>
       </c>
       <c r="R18">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="S18">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="T18">
         <v>2.73</v>
       </c>
       <c r="U18">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="V18">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W18">
         <v>1.08</v>
@@ -3276,7 +3276,7 @@
         <v>1.06</v>
       </c>
       <c r="Y18">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="Z18">
         <v>3.18</v>
@@ -3285,13 +3285,13 @@
         <v>2.02</v>
       </c>
       <c r="AB18">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AC18">
         <v>3.05</v>
       </c>
       <c r="AD18">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE18">
         <v>1.05</v>
@@ -3300,7 +3300,7 @@
         <v>1.87</v>
       </c>
       <c r="AG18">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AK18">
         <v>2.05</v>
@@ -3415,55 +3415,55 @@
         <v>3.75</v>
       </c>
       <c r="Q19">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="R19">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S19">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="T19">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="U19">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="V19">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W19">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y19">
         <v>1.38</v>
       </c>
       <c r="Z19">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="AA19">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="AB19">
         <v>1.71</v>
       </c>
       <c r="AC19">
-        <v>3.62</v>
+        <v>3.85</v>
       </c>
       <c r="AD19">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="AE19">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="AF19">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AG19">
-        <v>1.91</v>
+        <v>1.81</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK19">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         <v>1.28</v>
       </c>
       <c r="O21">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="P21">
-        <v>6.84</v>
+        <v>7.5</v>
       </c>
       <c r="Q21">
         <v>1.91</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -2609,7 +2609,7 @@
         <v>1.43</v>
       </c>
       <c r="T14">
-        <v>2.41</v>
+        <v>2.59</v>
       </c>
       <c r="U14">
         <v>3.3</v>
@@ -2636,13 +2636,13 @@
         <v>1.6</v>
       </c>
       <c r="AC14">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AD14">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="AE14">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="AF14">
         <v>2.15</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2763,10 +2763,10 @@
         <v>1.98</v>
       </c>
       <c r="Q15">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="R15">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="S15">
         <v>1.48</v>
@@ -2778,7 +2778,7 @@
         <v>3.15</v>
       </c>
       <c r="V15">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="W15">
         <v>1.02</v>
@@ -2799,7 +2799,7 @@
         <v>1.64</v>
       </c>
       <c r="AC15">
-        <v>3.95</v>
+        <v>3.94</v>
       </c>
       <c r="AD15">
         <v>1.17</v>
@@ -2811,7 +2811,7 @@
         <v>1.93</v>
       </c>
       <c r="AG15">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -3095,22 +3095,22 @@
         <v>2.1</v>
       </c>
       <c r="S17">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T17">
         <v>2.75</v>
       </c>
       <c r="U17">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="V17">
         <v>1.36</v>
       </c>
       <c r="W17">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y17">
         <v>1.33</v>
@@ -3122,13 +3122,13 @@
         <v>2.04</v>
       </c>
       <c r="AB17">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AC17">
         <v>3.6</v>
       </c>
       <c r="AD17">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE17">
         <v>1.07</v>
@@ -3246,13 +3246,13 @@
         <v>1.73</v>
       </c>
       <c r="O18">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P18">
         <v>5</v>
       </c>
       <c r="Q18">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="R18">
         <v>2.15</v>
@@ -3261,16 +3261,16 @@
         <v>1.41</v>
       </c>
       <c r="T18">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="U18">
-        <v>2.65</v>
+        <v>2.88</v>
       </c>
       <c r="V18">
         <v>1.43</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X18">
         <v>1.06</v>
@@ -3285,22 +3285,22 @@
         <v>2.02</v>
       </c>
       <c r="AB18">
-        <v>1.97</v>
+        <v>1.8</v>
       </c>
       <c r="AC18">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="AD18">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE18">
         <v>1.05</v>
       </c>
       <c r="AF18">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AG18">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3415,16 +3415,16 @@
         <v>3.75</v>
       </c>
       <c r="Q19">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R19">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S19">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T19">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="U19">
         <v>3.1</v>
@@ -3433,19 +3433,19 @@
         <v>1.32</v>
       </c>
       <c r="W19">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
         <v>1.06</v>
       </c>
       <c r="Y19">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="Z19">
         <v>2.85</v>
       </c>
       <c r="AA19">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AB19">
         <v>1.71</v>
@@ -3460,10 +3460,10 @@
         <v>1.06</v>
       </c>
       <c r="AF19">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="AG19">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AK19">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="O21">
-        <v>5</v>
+        <v>5.65</v>
       </c>
       <c r="P21">
-        <v>7.5</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="Q21">
         <v>1.91</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -2606,16 +2606,16 @@
         <v>2.1</v>
       </c>
       <c r="S14">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="T14">
         <v>2.59</v>
       </c>
       <c r="U14">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="V14">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W14">
         <v>1.03</v>
@@ -2633,7 +2633,7 @@
         <v>2.25</v>
       </c>
       <c r="AB14">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AC14">
         <v>4.1</v>
@@ -2642,7 +2642,7 @@
         <v>1.16</v>
       </c>
       <c r="AE14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF14">
         <v>2.15</v>
@@ -2763,71 +2763,71 @@
         <v>1.98</v>
       </c>
       <c r="Q15">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="R15">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="S15">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="T15">
-        <v>2.61</v>
+        <v>2.54</v>
       </c>
       <c r="U15">
         <v>3.15</v>
       </c>
       <c r="V15">
+        <v>1.3</v>
+      </c>
+      <c r="W15">
+        <v>1.03</v>
+      </c>
+      <c r="X15">
+        <v>1.07</v>
+      </c>
+      <c r="Y15">
+        <v>1.44</v>
+      </c>
+      <c r="Z15">
+        <v>2.7</v>
+      </c>
+      <c r="AA15">
+        <v>2.31</v>
+      </c>
+      <c r="AB15">
+        <v>1.63</v>
+      </c>
+      <c r="AC15">
+        <v>4.15</v>
+      </c>
+      <c r="AD15">
+        <v>1.2</v>
+      </c>
+      <c r="AE15">
+        <v>1.05</v>
+      </c>
+      <c r="AF15">
+        <v>1.95</v>
+      </c>
+      <c r="AG15">
+        <v>1.73</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15">
         <v>1.33</v>
       </c>
-      <c r="W15">
-        <v>1.02</v>
-      </c>
-      <c r="X15">
-        <v>1.04</v>
-      </c>
-      <c r="Y15">
-        <v>1.36</v>
-      </c>
-      <c r="Z15">
-        <v>2.95</v>
-      </c>
-      <c r="AA15">
-        <v>2.25</v>
-      </c>
-      <c r="AB15">
-        <v>1.64</v>
-      </c>
-      <c r="AC15">
-        <v>3.94</v>
-      </c>
-      <c r="AD15">
-        <v>1.17</v>
-      </c>
-      <c r="AE15">
-        <v>1.02</v>
-      </c>
-      <c r="AF15">
-        <v>1.93</v>
-      </c>
-      <c r="AG15">
-        <v>1.81</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ15">
-        <v>1.35</v>
-      </c>
       <c r="AK15">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3101,13 +3101,13 @@
         <v>2.75</v>
       </c>
       <c r="U17">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="V17">
         <v>1.36</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
         <v>1.03</v>
@@ -3119,10 +3119,10 @@
         <v>3.1</v>
       </c>
       <c r="AA17">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="AB17">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC17">
         <v>3.6</v>
@@ -3131,7 +3131,7 @@
         <v>1.24</v>
       </c>
       <c r="AE17">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF17">
         <v>1.83</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="O18">
         <v>3.6</v>
@@ -3252,25 +3252,25 @@
         <v>5</v>
       </c>
       <c r="Q18">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="R18">
-        <v>2.15</v>
+        <v>2.34</v>
       </c>
       <c r="S18">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="T18">
-        <v>2.62</v>
+        <v>3.18</v>
       </c>
       <c r="U18">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="V18">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W18">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="X18">
         <v>1.06</v>
@@ -3279,7 +3279,7 @@
         <v>1.27</v>
       </c>
       <c r="Z18">
-        <v>3.18</v>
+        <v>3.83</v>
       </c>
       <c r="AA18">
         <v>2.02</v>
@@ -3288,16 +3288,16 @@
         <v>1.8</v>
       </c>
       <c r="AC18">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="AD18">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AE18">
         <v>1.05</v>
       </c>
       <c r="AF18">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AG18">
         <v>1.83</v>
@@ -3316,7 +3316,7 @@
         <v>1.29</v>
       </c>
       <c r="AK18">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3415,22 +3415,22 @@
         <v>3.75</v>
       </c>
       <c r="Q19">
+        <v>2.6</v>
+      </c>
+      <c r="R19">
+        <v>2.08</v>
+      </c>
+      <c r="S19">
+        <v>1.43</v>
+      </c>
+      <c r="T19">
         <v>2.62</v>
       </c>
-      <c r="R19">
-        <v>2.1</v>
-      </c>
-      <c r="S19">
-        <v>1.4</v>
-      </c>
-      <c r="T19">
-        <v>2.7</v>
-      </c>
       <c r="U19">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="V19">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W19">
         <v>1.07</v>
@@ -3439,19 +3439,19 @@
         <v>1.06</v>
       </c>
       <c r="Y19">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="Z19">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AA19">
         <v>2.15</v>
       </c>
       <c r="AB19">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AC19">
-        <v>3.85</v>
+        <v>3.62</v>
       </c>
       <c r="AD19">
         <v>1.22</v>
@@ -3460,10 +3460,10 @@
         <v>1.06</v>
       </c>
       <c r="AF19">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AG19">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,7 +3476,7 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AK19">
         <v>1.79</v>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.7</v>
+        <v>1.63</v>
       </c>
       <c r="O20">
         <v>3.3</v>
@@ -3732,10 +3732,10 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="O21">
-        <v>5.65</v>
+        <v>5</v>
       </c>
       <c r="P21">
         <v>8.220000000000001</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -2609,7 +2609,7 @@
         <v>1.47</v>
       </c>
       <c r="T14">
-        <v>2.59</v>
+        <v>2.47</v>
       </c>
       <c r="U14">
         <v>3.25</v>
@@ -2624,7 +2624,7 @@
         <v>1.03</v>
       </c>
       <c r="Y14">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z14">
         <v>2.77</v>
@@ -2648,7 +2648,7 @@
         <v>2.15</v>
       </c>
       <c r="AG14">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK14">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2763,7 +2763,7 @@
         <v>1.98</v>
       </c>
       <c r="Q15">
-        <v>4.2</v>
+        <v>4.75</v>
       </c>
       <c r="R15">
         <v>1.95</v>
@@ -2781,22 +2781,22 @@
         <v>1.3</v>
       </c>
       <c r="W15">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X15">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
         <v>1.44</v>
       </c>
       <c r="Z15">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="AA15">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AB15">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="AC15">
         <v>4.15</v>
@@ -2805,7 +2805,7 @@
         <v>1.2</v>
       </c>
       <c r="AE15">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AF15">
         <v>1.95</v>
@@ -2827,7 +2827,7 @@
         <v>1.33</v>
       </c>
       <c r="AK15">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3569,13 +3569,13 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.63</v>
+        <v>1.77</v>
       </c>
       <c r="O20">
         <v>3.3</v>
       </c>
       <c r="P20">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="Q20">
         <v>0</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -1124,16 +1124,16 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.15</v>
+        <v>2.86</v>
       </c>
       <c r="O5">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P5">
         <v>2.2</v>
       </c>
       <c r="Q5">
-        <v>3.4</v>
+        <v>3.59</v>
       </c>
       <c r="R5">
         <v>2.25</v>
@@ -1145,40 +1145,40 @@
         <v>2.88</v>
       </c>
       <c r="U5">
-        <v>2.55</v>
+        <v>2.88</v>
       </c>
       <c r="V5">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W5">
         <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y5">
         <v>1.24</v>
       </c>
       <c r="Z5">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AA5">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AB5">
         <v>1.85</v>
       </c>
       <c r="AC5">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="AD5">
         <v>1.31</v>
       </c>
       <c r="AE5">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF5">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AG5">
         <v>2</v>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.7</v>
+        <v>1.29</v>
       </c>
       <c r="AK5">
         <v>1.3</v>
@@ -1287,25 +1287,25 @@
         </is>
       </c>
       <c r="N6">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="O6">
-        <v>4.15</v>
+        <v>4.25</v>
       </c>
       <c r="P6">
         <v>1.51</v>
       </c>
       <c r="Q6">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="R6">
         <v>2.4</v>
       </c>
       <c r="S6">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T6">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="U6">
         <v>2.56</v>
@@ -1314,10 +1314,10 @@
         <v>1.48</v>
       </c>
       <c r="W6">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
         <v>1.21</v>
@@ -1326,25 +1326,25 @@
         <v>3.62</v>
       </c>
       <c r="AA6">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AB6">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="AC6">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="AD6">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AE6">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AF6">
         <v>1.88</v>
       </c>
       <c r="AG6">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
         <v>2.55</v>
       </c>
       <c r="Q7">
-        <v>2.54</v>
+        <v>2.84</v>
       </c>
       <c r="R7">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S7">
         <v>1.25</v>
@@ -1471,13 +1471,13 @@
         <v>3.4</v>
       </c>
       <c r="U7">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="V7">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W7">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
         <v>1.04</v>
@@ -1486,28 +1486,28 @@
         <v>1.2</v>
       </c>
       <c r="Z7">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="AA7">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB7">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="AC7">
         <v>2.46</v>
       </c>
       <c r="AD7">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AE7">
         <v>1.15</v>
       </c>
       <c r="AF7">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AG7">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1619,19 +1619,19 @@
         <v>3.5</v>
       </c>
       <c r="P8">
-        <v>1.97</v>
+        <v>2.16</v>
       </c>
       <c r="Q8">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="R8">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S8">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T8">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="U8">
         <v>2.28</v>
@@ -1640,7 +1640,7 @@
         <v>1.53</v>
       </c>
       <c r="W8">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X8">
         <v>1</v>
@@ -1658,13 +1658,13 @@
         <v>2.12</v>
       </c>
       <c r="AC8">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="AD8">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AE8">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AF8">
         <v>1.56</v>
@@ -1776,34 +1776,34 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="O9">
-        <v>5.25</v>
+        <v>4.99</v>
       </c>
       <c r="P9">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="Q9">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="R9">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="S9">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="T9">
         <v>3.15</v>
       </c>
       <c r="U9">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="V9">
-        <v>1.45</v>
+        <v>1.55</v>
       </c>
       <c r="W9">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X9">
         <v>1.01</v>
@@ -1812,13 +1812,13 @@
         <v>1.2</v>
       </c>
       <c r="Z9">
-        <v>4.33</v>
+        <v>4.4</v>
       </c>
       <c r="AA9">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB9">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AC9">
         <v>2.5</v>
@@ -1827,13 +1827,13 @@
         <v>1.51</v>
       </c>
       <c r="AE9">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF9">
         <v>1.85</v>
       </c>
       <c r="AG9">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1849,7 +1849,7 @@
         <v>1.15</v>
       </c>
       <c r="AK9">
-        <v>2.99</v>
+        <v>2.75</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,13 +1939,13 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="O10">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="P10">
-        <v>5.73</v>
+        <v>5.5</v>
       </c>
       <c r="Q10">
         <v>1.97</v>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.16</v>
+        <v>1.09</v>
       </c>
       <c r="AK10">
         <v>2.18</v>
@@ -2105,22 +2105,22 @@
         <v>1.43</v>
       </c>
       <c r="O11">
-        <v>4.83</v>
+        <v>4.45</v>
       </c>
       <c r="P11">
-        <v>5.9</v>
+        <v>7.4</v>
       </c>
       <c r="Q11">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R11">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="S11">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="T11">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="U11">
         <v>2.27</v>
@@ -2132,22 +2132,22 @@
         <v>1.11</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y11">
         <v>1.2</v>
       </c>
       <c r="Z11">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA11">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB11">
         <v>2.26</v>
       </c>
       <c r="AC11">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="AD11">
         <v>1.45</v>
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.06</v>
+        <v>1.14</v>
       </c>
       <c r="AK11">
         <v>2.88</v>
@@ -2265,10 +2265,10 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="O12">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="P12">
         <v>4</v>
@@ -2277,7 +2277,7 @@
         <v>2.25</v>
       </c>
       <c r="R12">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="S12">
         <v>1.25</v>
@@ -2289,40 +2289,40 @@
         <v>2.22</v>
       </c>
       <c r="V12">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="W12">
         <v>1.12</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y12">
         <v>1.13</v>
       </c>
       <c r="Z12">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA12">
         <v>1.56</v>
       </c>
       <c r="AB12">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
       <c r="AC12">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="AD12">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AE12">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF12">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG12">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AK12">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,16 +2428,16 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="O13">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="P13">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="Q13">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="R13">
         <v>2.25</v>
@@ -2449,10 +2449,10 @@
         <v>3.25</v>
       </c>
       <c r="U13">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="V13">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="W13">
         <v>1.11</v>
@@ -2461,31 +2461,31 @@
         <v>1.01</v>
       </c>
       <c r="Y13">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z13">
-        <v>3.74</v>
+        <v>4</v>
       </c>
       <c r="AA13">
         <v>1.75</v>
       </c>
       <c r="AB13">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="AC13">
         <v>2.71</v>
       </c>
       <c r="AD13">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="AE13">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AF13">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AG13">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.58</v>
+        <v>3.83</v>
       </c>
       <c r="O14">
-        <v>3.68</v>
+        <v>3.25</v>
       </c>
       <c r="P14">
-        <v>5.91</v>
+        <v>1.98</v>
       </c>
       <c r="Q14">
-        <v>2.1</v>
+        <v>4.75</v>
       </c>
       <c r="R14">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S14">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="T14">
-        <v>2.47</v>
+        <v>2.54</v>
       </c>
       <c r="U14">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="V14">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W14">
+        <v>1.01</v>
+      </c>
+      <c r="X14">
+        <v>1.04</v>
+      </c>
+      <c r="Y14">
+        <v>1.44</v>
+      </c>
+      <c r="Z14">
+        <v>2.53</v>
+      </c>
+      <c r="AA14">
+        <v>2.33</v>
+      </c>
+      <c r="AB14">
+        <v>1.55</v>
+      </c>
+      <c r="AC14">
+        <v>4.15</v>
+      </c>
+      <c r="AD14">
+        <v>1.2</v>
+      </c>
+      <c r="AE14">
         <v>1.03</v>
       </c>
-      <c r="X14">
-        <v>1.03</v>
-      </c>
-      <c r="Y14">
-        <v>1.4</v>
-      </c>
-      <c r="Z14">
-        <v>2.77</v>
-      </c>
-      <c r="AA14">
-        <v>2.25</v>
-      </c>
-      <c r="AB14">
-        <v>1.61</v>
-      </c>
-      <c r="AC14">
-        <v>4.1</v>
-      </c>
-      <c r="AD14">
-        <v>1.16</v>
-      </c>
-      <c r="AE14">
-        <v>1.04</v>
-      </c>
       <c r="AF14">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AG14">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK14">
-        <v>2.28</v>
+        <v>1.22</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,64 +2754,64 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.83</v>
+        <v>1.58</v>
       </c>
       <c r="O15">
+        <v>3.68</v>
+      </c>
+      <c r="P15">
+        <v>5.91</v>
+      </c>
+      <c r="Q15">
+        <v>2.1</v>
+      </c>
+      <c r="R15">
+        <v>2.1</v>
+      </c>
+      <c r="S15">
+        <v>1.47</v>
+      </c>
+      <c r="T15">
+        <v>2.47</v>
+      </c>
+      <c r="U15">
         <v>3.25</v>
       </c>
-      <c r="P15">
-        <v>1.98</v>
-      </c>
-      <c r="Q15">
-        <v>4.75</v>
-      </c>
-      <c r="R15">
-        <v>1.95</v>
-      </c>
-      <c r="S15">
-        <v>1.5</v>
-      </c>
-      <c r="T15">
-        <v>2.54</v>
-      </c>
-      <c r="U15">
-        <v>3.15</v>
-      </c>
       <c r="V15">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W15">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
+        <v>1.03</v>
+      </c>
+      <c r="Y15">
+        <v>1.4</v>
+      </c>
+      <c r="Z15">
+        <v>2.77</v>
+      </c>
+      <c r="AA15">
+        <v>2.25</v>
+      </c>
+      <c r="AB15">
+        <v>1.61</v>
+      </c>
+      <c r="AC15">
+        <v>4.1</v>
+      </c>
+      <c r="AD15">
+        <v>1.16</v>
+      </c>
+      <c r="AE15">
         <v>1.04</v>
       </c>
-      <c r="Y15">
-        <v>1.44</v>
-      </c>
-      <c r="Z15">
-        <v>2.53</v>
-      </c>
-      <c r="AA15">
-        <v>2.33</v>
-      </c>
-      <c r="AB15">
-        <v>1.55</v>
-      </c>
-      <c r="AC15">
-        <v>4.15</v>
-      </c>
-      <c r="AD15">
-        <v>1.2</v>
-      </c>
-      <c r="AE15">
-        <v>1.03</v>
-      </c>
       <c r="AF15">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AG15">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK15">
-        <v>1.22</v>
+        <v>2.28</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3089,7 +3089,7 @@
         <v>0</v>
       </c>
       <c r="Q17">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R17">
         <v>2.1</v>
@@ -3098,40 +3098,40 @@
         <v>1.4</v>
       </c>
       <c r="T17">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U17">
-        <v>2.82</v>
+        <v>3.05</v>
       </c>
       <c r="V17">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="W17">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X17">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y17">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Z17">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AA17">
         <v>2.12</v>
       </c>
       <c r="AB17">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AC17">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="AD17">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE17">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF17">
         <v>1.83</v>
@@ -3252,34 +3252,34 @@
         <v>5</v>
       </c>
       <c r="Q18">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="R18">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="S18">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="T18">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="U18">
         <v>2.71</v>
       </c>
       <c r="V18">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="W18">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X18">
         <v>1.06</v>
       </c>
       <c r="Y18">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z18">
-        <v>3.83</v>
+        <v>3.84</v>
       </c>
       <c r="AA18">
         <v>2.02</v>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AK18">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3442,7 +3442,7 @@
         <v>1.38</v>
       </c>
       <c r="Z19">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="AA19">
         <v>2.15</v>
@@ -3457,13 +3457,13 @@
         <v>1.22</v>
       </c>
       <c r="AE19">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF19">
         <v>1.85</v>
       </c>
       <c r="AG19">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="O21">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="P21">
-        <v>8.220000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="Q21">
         <v>1.91</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -1450,19 +1450,19 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.58</v>
+        <v>2.16</v>
       </c>
       <c r="O7">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="P7">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="Q7">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="R7">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="S7">
         <v>1.25</v>
@@ -1480,7 +1480,7 @@
         <v>1.08</v>
       </c>
       <c r="X7">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
         <v>1.2</v>
@@ -1489,10 +1489,10 @@
         <v>4.3</v>
       </c>
       <c r="AA7">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AB7">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="AC7">
         <v>2.46</v>
@@ -1501,7 +1501,7 @@
         <v>1.5</v>
       </c>
       <c r="AE7">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AF7">
         <v>1.5</v>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
       <c r="AK7">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,16 +1613,16 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O8">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="P8">
-        <v>2.16</v>
+        <v>2.01</v>
       </c>
       <c r="Q8">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="R8">
         <v>2.3</v>
@@ -1631,7 +1631,7 @@
         <v>1.31</v>
       </c>
       <c r="T8">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="U8">
         <v>2.28</v>
@@ -1640,25 +1640,25 @@
         <v>1.53</v>
       </c>
       <c r="W8">
-        <v>1.09</v>
+        <v>1.12</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y8">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z8">
-        <v>4.28</v>
+        <v>4.31</v>
       </c>
       <c r="AA8">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AB8">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AC8">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="AD8">
         <v>1.41</v>
@@ -1667,10 +1667,10 @@
         <v>1.13</v>
       </c>
       <c r="AF8">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AG8">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,65 +3080,65 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q17">
-        <v>2.75</v>
+        <v>2.28</v>
       </c>
       <c r="R17">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S17">
         <v>1.4</v>
       </c>
       <c r="T17">
-        <v>2.53</v>
+        <v>3.17</v>
       </c>
       <c r="U17">
-        <v>3.05</v>
+        <v>2.71</v>
       </c>
       <c r="V17">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="W17">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="X17">
         <v>1.06</v>
       </c>
       <c r="Y17">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z17">
-        <v>2.9</v>
+        <v>3.84</v>
       </c>
       <c r="AA17">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="AB17">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AC17">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="AD17">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AE17">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AF17">
+        <v>1.71</v>
+      </c>
+      <c r="AG17">
         <v>1.83</v>
       </c>
-      <c r="AG17">
-        <v>1.85</v>
-      </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="AK17">
-        <v>1.69</v>
+        <v>2.05</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,65 +3243,65 @@
         </is>
       </c>
       <c r="N18">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="O18">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P18">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="Q18">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="R18">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="S18">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T18">
-        <v>3.17</v>
+        <v>2.62</v>
       </c>
       <c r="U18">
-        <v>2.71</v>
+        <v>2.9</v>
       </c>
       <c r="V18">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="W18">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X18">
         <v>1.06</v>
       </c>
       <c r="Y18">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="Z18">
-        <v>3.84</v>
+        <v>3</v>
       </c>
       <c r="AA18">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="AB18">
+        <v>1.68</v>
+      </c>
+      <c r="AC18">
+        <v>3.62</v>
+      </c>
+      <c r="AD18">
+        <v>1.22</v>
+      </c>
+      <c r="AE18">
+        <v>1.04</v>
+      </c>
+      <c r="AF18">
+        <v>1.85</v>
+      </c>
+      <c r="AG18">
         <v>1.8</v>
       </c>
-      <c r="AC18">
-        <v>3.05</v>
-      </c>
-      <c r="AD18">
-        <v>1.38</v>
-      </c>
-      <c r="AE18">
-        <v>1.05</v>
-      </c>
-      <c r="AF18">
-        <v>1.71</v>
-      </c>
-      <c r="AG18">
-        <v>1.83</v>
-      </c>
       <c r="AH18" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AK18">
-        <v>2.05</v>
+        <v>1.79</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,65 +3406,65 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P19">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="Q19">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="R19">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="S19">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T19">
-        <v>2.62</v>
+        <v>2.53</v>
       </c>
       <c r="U19">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="V19">
         <v>1.33</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X19">
         <v>1.06</v>
       </c>
       <c r="Y19">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="Z19">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AA19">
-        <v>2.15</v>
+        <v>2.12</v>
       </c>
       <c r="AB19">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AC19">
-        <v>3.62</v>
+        <v>3.9</v>
       </c>
       <c r="AD19">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE19">
         <v>1.04</v>
       </c>
       <c r="AF19">
+        <v>1.83</v>
+      </c>
+      <c r="AG19">
         <v>1.85</v>
       </c>
-      <c r="AG19">
-        <v>1.8</v>
-      </c>
       <c r="AH19" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AK19">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="AL19">
         <v>0</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S2">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="T2">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U2">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="V2">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W2">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X2">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y2">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z2">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AA2">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB2">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AC2">
-        <v>0</v>
+        <v>4.11</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE2">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG2">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK2">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="P3">
-        <v>0</v>
+        <v>5.87</v>
       </c>
       <c r="Q3">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W3">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA3">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB3">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC3">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE3">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK3">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>4.94</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="T4">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="V4">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W4">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y4">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z4">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AA4">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB4">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>4.28</v>
       </c>
       <c r="AD4">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE4">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF4">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG4">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Botafogo</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Grêmio</t>
         </is>
       </c>
       <c r="G16">
@@ -2917,64 +2917,64 @@
         </is>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T16">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="U16">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y16">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="Z16">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA16">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB16">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AC16">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AD16">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE16">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF16">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG16">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AK16">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Botafogo</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grêmio</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,80 +3080,80 @@
         </is>
       </c>
       <c r="N17">
-        <v>1.72</v>
+        <v>2.05</v>
       </c>
       <c r="O17">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="P17">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="Q17">
-        <v>2.28</v>
+        <v>2.6</v>
       </c>
       <c r="R17">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="S17">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T17">
-        <v>3.17</v>
+        <v>2.62</v>
       </c>
       <c r="U17">
-        <v>2.71</v>
+        <v>2.9</v>
       </c>
       <c r="V17">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="W17">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
+        <v>1.05</v>
+      </c>
+      <c r="Y17">
+        <v>1.38</v>
+      </c>
+      <c r="Z17">
+        <v>3.05</v>
+      </c>
+      <c r="AA17">
+        <v>2.16</v>
+      </c>
+      <c r="AB17">
+        <v>1.68</v>
+      </c>
+      <c r="AC17">
+        <v>3.95</v>
+      </c>
+      <c r="AD17">
+        <v>1.23</v>
+      </c>
+      <c r="AE17">
         <v>1.06</v>
       </c>
-      <c r="Y17">
+      <c r="AF17">
+        <v>1.9</v>
+      </c>
+      <c r="AG17">
+        <v>1.81</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ17">
         <v>1.3</v>
       </c>
-      <c r="Z17">
-        <v>3.84</v>
-      </c>
-      <c r="AA17">
-        <v>2.02</v>
-      </c>
-      <c r="AB17">
+      <c r="AK17">
         <v>1.8</v>
-      </c>
-      <c r="AC17">
-        <v>3.05</v>
-      </c>
-      <c r="AD17">
-        <v>1.38</v>
-      </c>
-      <c r="AE17">
-        <v>1.05</v>
-      </c>
-      <c r="AF17">
-        <v>1.71</v>
-      </c>
-      <c r="AG17">
-        <v>1.83</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ17">
-        <v>1.26</v>
-      </c>
-      <c r="AK17">
-        <v>2.05</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,31 +3243,31 @@
         </is>
       </c>
       <c r="N18">
+        <v>3.1</v>
+      </c>
+      <c r="O18">
+        <v>3.2</v>
+      </c>
+      <c r="P18">
+        <v>2.37</v>
+      </c>
+      <c r="Q18">
+        <v>3.4</v>
+      </c>
+      <c r="R18">
         <v>2.05</v>
       </c>
-      <c r="O18">
-        <v>3.3</v>
-      </c>
-      <c r="P18">
-        <v>3.75</v>
-      </c>
-      <c r="Q18">
-        <v>2.6</v>
-      </c>
-      <c r="R18">
-        <v>2.08</v>
-      </c>
       <c r="S18">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T18">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U18">
         <v>2.9</v>
       </c>
       <c r="V18">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W18">
         <v>1.07</v>
@@ -3276,31 +3276,31 @@
         <v>1.06</v>
       </c>
       <c r="Y18">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="Z18">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AA18">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AB18">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AC18">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="AD18">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE18">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF18">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AG18">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK18">
-        <v>1.79</v>
+        <v>1.35</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3402,20 +3402,20 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="Q19">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R19">
         <v>2.1</v>
@@ -3424,46 +3424,46 @@
         <v>1.4</v>
       </c>
       <c r="T19">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="U19">
-        <v>3.05</v>
+        <v>2.82</v>
       </c>
       <c r="V19">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W19">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X19">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="Z19">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AA19">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB19">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AC19">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AD19">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE19">
         <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG19">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AK19">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="O21">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="P21">
-        <v>7.9</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="Q21">
         <v>1.91</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2.02</v>
+        <v>1.76</v>
       </c>
       <c r="O2">
-        <v>3.2</v>
+        <v>3.57</v>
       </c>
       <c r="P2">
-        <v>3.3</v>
+        <v>4.46</v>
       </c>
       <c r="Q2">
-        <v>2.68</v>
+        <v>2.27</v>
       </c>
       <c r="R2">
+        <v>2.05</v>
+      </c>
+      <c r="S2">
+        <v>1.37</v>
+      </c>
+      <c r="T2">
+        <v>2.52</v>
+      </c>
+      <c r="U2">
+        <v>2.92</v>
+      </c>
+      <c r="V2">
+        <v>1.32</v>
+      </c>
+      <c r="W2">
+        <v>1.07</v>
+      </c>
+      <c r="X2">
+        <v>1.05</v>
+      </c>
+      <c r="Y2">
+        <v>1.29</v>
+      </c>
+      <c r="Z2">
+        <v>3.25</v>
+      </c>
+      <c r="AA2">
         <v>2</v>
       </c>
-      <c r="S2">
-        <v>1.41</v>
-      </c>
-      <c r="T2">
-        <v>2.56</v>
-      </c>
-      <c r="U2">
-        <v>3.04</v>
-      </c>
-      <c r="V2">
-        <v>1.3</v>
-      </c>
-      <c r="W2">
+      <c r="AB2">
+        <v>1.8</v>
+      </c>
+      <c r="AC2">
+        <v>3.8</v>
+      </c>
+      <c r="AD2">
+        <v>1.25</v>
+      </c>
+      <c r="AE2">
         <v>1.04</v>
       </c>
-      <c r="X2">
-        <v>1.02</v>
-      </c>
-      <c r="Y2">
-        <v>1.35</v>
-      </c>
-      <c r="Z2">
-        <v>3.06</v>
-      </c>
-      <c r="AA2">
-        <v>2.11</v>
-      </c>
-      <c r="AB2">
-        <v>1.68</v>
-      </c>
-      <c r="AC2">
-        <v>4.11</v>
-      </c>
-      <c r="AD2">
-        <v>1.22</v>
-      </c>
-      <c r="AE2">
-        <v>1.03</v>
-      </c>
       <c r="AF2">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG2">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.29</v>
+        <v>1.17</v>
       </c>
       <c r="AK2">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G3">
@@ -798,80 +798,80 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="O3">
-        <v>3.74</v>
+        <v>3.4</v>
       </c>
       <c r="P3">
-        <v>5.87</v>
+        <v>5.3</v>
       </c>
       <c r="Q3">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="R3">
+        <v>2.19</v>
+      </c>
+      <c r="S3">
+        <v>1.4</v>
+      </c>
+      <c r="T3">
+        <v>2.65</v>
+      </c>
+      <c r="U3">
+        <v>3.06</v>
+      </c>
+      <c r="V3">
+        <v>1.3</v>
+      </c>
+      <c r="W3">
+        <v>1.07</v>
+      </c>
+      <c r="X3">
+        <v>1.03</v>
+      </c>
+      <c r="Y3">
+        <v>1.35</v>
+      </c>
+      <c r="Z3">
+        <v>3.01</v>
+      </c>
+      <c r="AA3">
+        <v>2.11</v>
+      </c>
+      <c r="AB3">
+        <v>1.68</v>
+      </c>
+      <c r="AC3">
+        <v>4.34</v>
+      </c>
+      <c r="AD3">
+        <v>1.22</v>
+      </c>
+      <c r="AE3">
+        <v>1.03</v>
+      </c>
+      <c r="AF3">
+        <v>2</v>
+      </c>
+      <c r="AG3">
+        <v>1.7</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3">
+        <v>1.11</v>
+      </c>
+      <c r="AK3">
         <v>2.2</v>
-      </c>
-      <c r="S3">
-        <v>1.36</v>
-      </c>
-      <c r="T3">
-        <v>2.88</v>
-      </c>
-      <c r="U3">
-        <v>2.88</v>
-      </c>
-      <c r="V3">
-        <v>1.33</v>
-      </c>
-      <c r="W3">
-        <v>1.06</v>
-      </c>
-      <c r="X3">
-        <v>1.01</v>
-      </c>
-      <c r="Y3">
-        <v>1.3</v>
-      </c>
-      <c r="Z3">
-        <v>3.4</v>
-      </c>
-      <c r="AA3">
-        <v>2</v>
-      </c>
-      <c r="AB3">
-        <v>1.8</v>
-      </c>
-      <c r="AC3">
-        <v>3.64</v>
-      </c>
-      <c r="AD3">
-        <v>1.26</v>
-      </c>
-      <c r="AE3">
-        <v>1.05</v>
-      </c>
-      <c r="AF3">
-        <v>1.97</v>
-      </c>
-      <c r="AG3">
-        <v>1.69</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3">
-        <v>1.2</v>
-      </c>
-      <c r="AK3">
-        <v>2.25</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.7</v>
+        <v>1.98</v>
       </c>
       <c r="O4">
-        <v>3.55</v>
+        <v>3</v>
       </c>
       <c r="P4">
-        <v>4.94</v>
+        <v>3.6</v>
       </c>
       <c r="Q4">
-        <v>2.3</v>
+        <v>2.76</v>
       </c>
       <c r="R4">
-        <v>2.02</v>
+        <v>2.07</v>
       </c>
       <c r="S4">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="T4">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="U4">
-        <v>3.12</v>
+        <v>3.19</v>
       </c>
       <c r="V4">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="W4">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="X4">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y4">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="Z4">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="AA4">
-        <v>2.17</v>
+        <v>2.26</v>
       </c>
       <c r="AB4">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AC4">
-        <v>4.28</v>
+        <v>4.7</v>
       </c>
       <c r="AD4">
         <v>1.2</v>
       </c>
       <c r="AE4">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF4">
-        <v>2.01</v>
+        <v>1.93</v>
       </c>
       <c r="AG4">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AK4">
-        <v>2.03</v>
+        <v>1.7</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>2.86</v>
+        <v>3.18</v>
       </c>
       <c r="O5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P5">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Q5">
-        <v>3.59</v>
+        <v>3.72</v>
       </c>
       <c r="R5">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S5">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="T5">
         <v>2.88</v>
       </c>
       <c r="U5">
-        <v>2.88</v>
+        <v>2.73</v>
       </c>
       <c r="V5">
         <v>1.42</v>
       </c>
       <c r="W5">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y5">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z5">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="AA5">
-        <v>1.94</v>
+        <v>1.87</v>
       </c>
       <c r="AB5">
         <v>1.85</v>
       </c>
       <c r="AC5">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AD5">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AE5">
         <v>1.1</v>
       </c>
       <c r="AF5">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AG5">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,7 +1194,7 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK5">
         <v>1.3</v>
@@ -1287,37 +1287,37 @@
         </is>
       </c>
       <c r="N6">
-        <v>6</v>
+        <v>5.1</v>
       </c>
       <c r="O6">
-        <v>4.25</v>
+        <v>4.8</v>
       </c>
       <c r="P6">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Q6">
-        <v>5.25</v>
+        <v>5.73</v>
       </c>
       <c r="R6">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="S6">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="T6">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="U6">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="V6">
         <v>1.48</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
         <v>1.21</v>
@@ -1326,25 +1326,25 @@
         <v>3.62</v>
       </c>
       <c r="AA6">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="AB6">
-        <v>2.01</v>
+        <v>2.1</v>
       </c>
       <c r="AC6">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="AD6">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="AE6">
         <v>1.15</v>
       </c>
       <c r="AF6">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AG6">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>1.17</v>
+        <v>2.61</v>
       </c>
       <c r="AK6">
         <v>1.1</v>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>United Nordic</t>
+          <t>Norrköping</t>
         </is>
       </c>
       <c r="G7">
@@ -1450,64 +1450,64 @@
         </is>
       </c>
       <c r="N7">
-        <v>2.16</v>
+        <v>3.05</v>
       </c>
       <c r="O7">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="P7">
-        <v>2.48</v>
+        <v>2.12</v>
       </c>
       <c r="Q7">
-        <v>2.81</v>
+        <v>3.77</v>
       </c>
       <c r="R7">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S7">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T7">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="U7">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="V7">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="W7">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="X7">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z7">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="AA7">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AB7">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AC7">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="AD7">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AE7">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="AF7">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AG7">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="AK7">
-        <v>1.54</v>
+        <v>1.32</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1581,12 +1581,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norrköping</t>
+          <t>United Nordic</t>
         </is>
       </c>
       <c r="G8">
@@ -1613,64 +1613,64 @@
         </is>
       </c>
       <c r="N8">
-        <v>3.3</v>
+        <v>2.16</v>
       </c>
       <c r="O8">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="P8">
-        <v>2.01</v>
+        <v>2.48</v>
       </c>
       <c r="Q8">
-        <v>3.94</v>
+        <v>2.54</v>
       </c>
       <c r="R8">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S8">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="T8">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="U8">
-        <v>2.28</v>
+        <v>2.39</v>
       </c>
       <c r="V8">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="W8">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X8">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z8">
-        <v>4.31</v>
+        <v>4.5</v>
       </c>
       <c r="AA8">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AB8">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AC8">
-        <v>2.52</v>
+        <v>2.46</v>
       </c>
       <c r="AD8">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE8">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AF8">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AG8">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AK8">
-        <v>1.28</v>
+        <v>1.54</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,64 +1776,64 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="O9">
-        <v>4.99</v>
+        <v>4.7</v>
       </c>
       <c r="P9">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="R9">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="S9">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="T9">
-        <v>3.15</v>
+        <v>3.42</v>
       </c>
       <c r="U9">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="V9">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W9">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="X9">
         <v>1.01</v>
       </c>
       <c r="Y9">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z9">
         <v>4.4</v>
       </c>
       <c r="AA9">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="AB9">
         <v>2.25</v>
       </c>
       <c r="AC9">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="AD9">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="AE9">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="AF9">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG9">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.15</v>
+        <v>1.11</v>
       </c>
       <c r="AK9">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,46 +1939,46 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="O10">
         <v>4.05</v>
       </c>
       <c r="P10">
-        <v>5.5</v>
+        <v>5.15</v>
       </c>
       <c r="Q10">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
       <c r="R10">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U10">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V10">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z10">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="AA10">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AB10">
         <v>2.06</v>
@@ -1990,13 +1990,13 @@
         <v>1.41</v>
       </c>
       <c r="AE10">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF10">
-        <v>1.72</v>
+        <v>1.67</v>
       </c>
       <c r="AG10">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="AK10">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="O11">
         <v>4.45</v>
       </c>
       <c r="P11">
-        <v>7.4</v>
+        <v>6.3</v>
       </c>
       <c r="Q11">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R11">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="S11">
         <v>1.3</v>
       </c>
       <c r="T11">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="U11">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="V11">
         <v>1.54</v>
       </c>
       <c r="W11">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X11">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y11">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="Z11">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="AA11">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AB11">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AC11">
-        <v>2.75</v>
+        <v>2.39</v>
       </c>
       <c r="AD11">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE11">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AF11">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="AG11">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AK11">
-        <v>2.88</v>
+        <v>2.59</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,34 +2265,34 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="O12">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="P12">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Q12">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="R12">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="S12">
         <v>1.25</v>
       </c>
       <c r="T12">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="U12">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="V12">
         <v>1.59</v>
       </c>
       <c r="W12">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X12">
         <v>1.01</v>
@@ -2301,22 +2301,22 @@
         <v>1.13</v>
       </c>
       <c r="Z12">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="AA12">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="AB12">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="AC12">
-        <v>2.45</v>
+        <v>2.31</v>
       </c>
       <c r="AD12">
         <v>1.53</v>
       </c>
       <c r="AE12">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AF12">
         <v>1.52</v>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="AK12">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,16 +2428,16 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="O13">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="P13">
-        <v>4</v>
+        <v>4.07</v>
       </c>
       <c r="Q13">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="R13">
         <v>2.25</v>
@@ -2449,43 +2449,43 @@
         <v>3.25</v>
       </c>
       <c r="U13">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="V13">
         <v>1.51</v>
       </c>
       <c r="W13">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X13">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y13">
         <v>1.2</v>
       </c>
       <c r="Z13">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="AA13">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AB13">
         <v>2.05</v>
       </c>
       <c r="AC13">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="AD13">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AE13">
         <v>1.14</v>
       </c>
       <c r="AF13">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AG13">
-        <v>2.05</v>
+        <v>1.98</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AK13">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2559,12 +2559,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Juventude</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G14">
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>3.83</v>
+        <v>1.57</v>
       </c>
       <c r="O14">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="P14">
-        <v>1.98</v>
+        <v>6.44</v>
       </c>
       <c r="Q14">
-        <v>4.75</v>
+        <v>2.16</v>
       </c>
       <c r="R14">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="S14">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T14">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="U14">
         <v>3.15</v>
       </c>
       <c r="V14">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W14">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X14">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y14">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Z14">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="AA14">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="AB14">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AC14">
-        <v>4.15</v>
+        <v>4.33</v>
       </c>
       <c r="AD14">
         <v>1.2</v>
       </c>
       <c r="AE14">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF14">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AG14">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AK14">
-        <v>1.22</v>
+        <v>2.4</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Juventude</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="G15">
@@ -2754,28 +2754,28 @@
         </is>
       </c>
       <c r="N15">
-        <v>1.58</v>
+        <v>4.06</v>
       </c>
       <c r="O15">
-        <v>3.68</v>
+        <v>3.12</v>
       </c>
       <c r="P15">
-        <v>5.91</v>
+        <v>1.97</v>
       </c>
       <c r="Q15">
-        <v>2.1</v>
+        <v>4.97</v>
       </c>
       <c r="R15">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="S15">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="T15">
-        <v>2.47</v>
+        <v>2.36</v>
       </c>
       <c r="U15">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="V15">
         <v>1.28</v>
@@ -2784,19 +2784,19 @@
         <v>1.03</v>
       </c>
       <c r="X15">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y15">
         <v>1.4</v>
       </c>
       <c r="Z15">
-        <v>2.77</v>
+        <v>2.88</v>
       </c>
       <c r="AA15">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="AB15">
-        <v>1.61</v>
+        <v>1.57</v>
       </c>
       <c r="AC15">
         <v>4.1</v>
@@ -2805,13 +2805,13 @@
         <v>1.16</v>
       </c>
       <c r="AE15">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF15">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="AG15">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.26</v>
+        <v>1.73</v>
       </c>
       <c r="AK15">
-        <v>2.28</v>
+        <v>1.21</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G18">
@@ -3239,23 +3239,23 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N18">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="O18">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>2.37</v>
+        <v>3.4</v>
       </c>
       <c r="Q18">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="R18">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S18">
         <v>1.4</v>
@@ -3264,43 +3264,43 @@
         <v>2.75</v>
       </c>
       <c r="U18">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="V18">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W18">
         <v>1.07</v>
       </c>
       <c r="X18">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="Y18">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="Z18">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="AA18">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AB18">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC18">
         <v>3.6</v>
       </c>
       <c r="AD18">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE18">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF18">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AG18">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AK18">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G19">
@@ -3402,23 +3402,23 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N19">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="O19">
+        <v>3.2</v>
+      </c>
+      <c r="P19">
+        <v>2.37</v>
+      </c>
+      <c r="Q19">
         <v>3.4</v>
       </c>
-      <c r="P19">
-        <v>3.4</v>
-      </c>
-      <c r="Q19">
-        <v>2.7</v>
-      </c>
       <c r="R19">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S19">
         <v>1.4</v>
@@ -3427,43 +3427,43 @@
         <v>2.75</v>
       </c>
       <c r="U19">
-        <v>2.82</v>
+        <v>2.9</v>
       </c>
       <c r="V19">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W19">
         <v>1.07</v>
       </c>
       <c r="X19">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y19">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="Z19">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="AA19">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AB19">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC19">
         <v>3.6</v>
       </c>
       <c r="AD19">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE19">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF19">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AG19">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="AK19">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,43 +3569,43 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="O20">
         <v>3.3</v>
       </c>
       <c r="P20">
-        <v>4.2</v>
+        <v>4.54</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA20">
         <v>2.15</v>
@@ -3614,19 +3614,19 @@
         <v>1.66</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.29</v>
+        <v>1.48</v>
       </c>
       <c r="O21">
+        <v>4.2</v>
+      </c>
+      <c r="P21">
         <v>5</v>
-      </c>
-      <c r="P21">
-        <v>8.220000000000001</v>
       </c>
       <c r="Q21">
         <v>1.91</v>
@@ -3774,7 +3774,7 @@
         <v>1.73</v>
       </c>
       <c r="AB21">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AC21">
         <v>2.35</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="O2">
-        <v>3.57</v>
+        <v>3.4</v>
       </c>
       <c r="P2">
-        <v>4.46</v>
+        <v>5.3</v>
       </c>
       <c r="Q2">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
       <c r="R2">
-        <v>2.05</v>
+        <v>2.19</v>
       </c>
       <c r="S2">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
-        <v>2.52</v>
+        <v>2.65</v>
       </c>
       <c r="U2">
-        <v>2.92</v>
+        <v>3.06</v>
       </c>
       <c r="V2">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="W2">
         <v>1.07</v>
       </c>
       <c r="X2">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y2">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="Z2">
-        <v>3.25</v>
+        <v>3.01</v>
       </c>
       <c r="AA2">
+        <v>2.11</v>
+      </c>
+      <c r="AB2">
+        <v>1.68</v>
+      </c>
+      <c r="AC2">
+        <v>4.34</v>
+      </c>
+      <c r="AD2">
+        <v>1.22</v>
+      </c>
+      <c r="AE2">
+        <v>1.03</v>
+      </c>
+      <c r="AF2">
         <v>2</v>
       </c>
-      <c r="AB2">
-        <v>1.8</v>
-      </c>
-      <c r="AC2">
-        <v>3.8</v>
-      </c>
-      <c r="AD2">
-        <v>1.25</v>
-      </c>
-      <c r="AE2">
-        <v>1.04</v>
-      </c>
-      <c r="AF2">
-        <v>1.85</v>
-      </c>
       <c r="AG2">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.17</v>
+        <v>1.11</v>
       </c>
       <c r="AK2">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G3">
@@ -798,80 +798,80 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.6</v>
+        <v>1.98</v>
       </c>
       <c r="O3">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="P3">
-        <v>5.3</v>
+        <v>3.6</v>
       </c>
       <c r="Q3">
-        <v>2.15</v>
+        <v>2.76</v>
       </c>
       <c r="R3">
-        <v>2.19</v>
+        <v>2.07</v>
       </c>
       <c r="S3">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="T3">
-        <v>2.65</v>
+        <v>2.56</v>
       </c>
       <c r="U3">
-        <v>3.06</v>
+        <v>3.19</v>
       </c>
       <c r="V3">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W3">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X3">
         <v>1.03</v>
       </c>
       <c r="Y3">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="Z3">
-        <v>3.01</v>
+        <v>3.08</v>
       </c>
       <c r="AA3">
-        <v>2.11</v>
+        <v>2.26</v>
       </c>
       <c r="AB3">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AC3">
-        <v>4.34</v>
+        <v>4.7</v>
       </c>
       <c r="AD3">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE3">
         <v>1.03</v>
       </c>
       <c r="AF3">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AG3">
+        <v>1.78</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ3">
+        <v>1.33</v>
+      </c>
+      <c r="AK3">
         <v>1.7</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3">
-        <v>1.11</v>
-      </c>
-      <c r="AK3">
-        <v>2.2</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G4">
@@ -961,61 +961,61 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.98</v>
+        <v>1.76</v>
       </c>
       <c r="O4">
-        <v>3</v>
+        <v>3.57</v>
       </c>
       <c r="P4">
-        <v>3.6</v>
+        <v>4.46</v>
       </c>
       <c r="Q4">
-        <v>2.76</v>
+        <v>2.27</v>
       </c>
       <c r="R4">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="S4">
-        <v>1.46</v>
+        <v>1.37</v>
       </c>
       <c r="T4">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="U4">
-        <v>3.19</v>
+        <v>2.92</v>
       </c>
       <c r="V4">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W4">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="X4">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y4">
-        <v>1.39</v>
+        <v>1.29</v>
       </c>
       <c r="Z4">
-        <v>3.08</v>
+        <v>3.25</v>
       </c>
       <c r="AA4">
-        <v>2.26</v>
+        <v>2</v>
       </c>
       <c r="AB4">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AC4">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="AD4">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE4">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF4">
-        <v>1.93</v>
+        <v>1.85</v>
       </c>
       <c r="AG4">
         <v>1.78</v>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AK4">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -2591,31 +2591,31 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="O14">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P14">
-        <v>6.44</v>
+        <v>5.5</v>
       </c>
       <c r="Q14">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="R14">
         <v>2.14</v>
       </c>
       <c r="S14">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="T14">
         <v>2.44</v>
       </c>
       <c r="U14">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="V14">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W14">
         <v>1</v>
@@ -2630,10 +2630,10 @@
         <v>2.75</v>
       </c>
       <c r="AA14">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AB14">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="AC14">
         <v>4.33</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.2</v>
+        <v>1.26</v>
       </c>
       <c r="AK14">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,19 +2754,19 @@
         </is>
       </c>
       <c r="N15">
-        <v>4.06</v>
+        <v>3.6</v>
       </c>
       <c r="O15">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="P15">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q15">
-        <v>4.97</v>
+        <v>4.2</v>
       </c>
       <c r="R15">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="S15">
         <v>1.45</v>
@@ -2778,22 +2778,22 @@
         <v>3.2</v>
       </c>
       <c r="V15">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W15">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X15">
         <v>1.05</v>
       </c>
       <c r="Y15">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="Z15">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AA15">
-        <v>2.29</v>
+        <v>2.35</v>
       </c>
       <c r="AB15">
         <v>1.57</v>
@@ -2802,16 +2802,16 @@
         <v>4.1</v>
       </c>
       <c r="AD15">
-        <v>1.16</v>
+        <v>1.21</v>
       </c>
       <c r="AE15">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="AF15">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="AG15">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="AK15">
         <v>1.21</v>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
       <c r="N16">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="O16">
         <v>3.5</v>
@@ -2926,19 +2926,19 @@
         <v>5</v>
       </c>
       <c r="Q16">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="R16">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="S16">
         <v>1.4</v>
       </c>
       <c r="T16">
-        <v>3.17</v>
+        <v>2.73</v>
       </c>
       <c r="U16">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="V16">
         <v>1.36</v>
@@ -2950,25 +2950,25 @@
         <v>1</v>
       </c>
       <c r="Y16">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="Z16">
-        <v>3.18</v>
+        <v>3.95</v>
       </c>
       <c r="AA16">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AB16">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AC16">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="AD16">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE16">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AF16">
         <v>1.87</v>
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="AJ16">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AK16">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="O17">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P17">
+        <v>2.37</v>
+      </c>
+      <c r="Q17">
         <v>3.75</v>
       </c>
-      <c r="Q17">
-        <v>2.6</v>
-      </c>
       <c r="R17">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="S17">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T17">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="U17">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="V17">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W17">
         <v>1.07</v>
       </c>
       <c r="X17">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y17">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="Z17">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="AA17">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="AB17">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AC17">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="AD17">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AE17">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="AF17">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AG17">
-        <v>1.81</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AK17">
-        <v>1.8</v>
+        <v>1.37</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G18">
@@ -3239,56 +3239,56 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N18">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P18">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="Q18">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="R18">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S18">
         <v>1.4</v>
       </c>
       <c r="T18">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="U18">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="V18">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W18">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X18">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y18">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z18">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA18">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AB18">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC18">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="AD18">
         <v>1.23</v>
@@ -3300,7 +3300,7 @@
         <v>1.85</v>
       </c>
       <c r="AG18">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AK18">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G19">
@@ -3402,68 +3402,68 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N19">
+        <v>2.1</v>
+      </c>
+      <c r="O19">
+        <v>3.4</v>
+      </c>
+      <c r="P19">
+        <v>3.4</v>
+      </c>
+      <c r="Q19">
+        <v>2.75</v>
+      </c>
+      <c r="R19">
+        <v>2.1</v>
+      </c>
+      <c r="S19">
+        <v>1.44</v>
+      </c>
+      <c r="T19">
+        <v>2.65</v>
+      </c>
+      <c r="U19">
+        <v>2.88</v>
+      </c>
+      <c r="V19">
+        <v>1.36</v>
+      </c>
+      <c r="W19">
+        <v>1.05</v>
+      </c>
+      <c r="X19">
+        <v>1.05</v>
+      </c>
+      <c r="Y19">
+        <v>1.35</v>
+      </c>
+      <c r="Z19">
         <v>3.1</v>
       </c>
-      <c r="O19">
-        <v>3.2</v>
-      </c>
-      <c r="P19">
-        <v>2.37</v>
-      </c>
-      <c r="Q19">
-        <v>3.4</v>
-      </c>
-      <c r="R19">
-        <v>2.05</v>
-      </c>
-      <c r="S19">
-        <v>1.4</v>
-      </c>
-      <c r="T19">
-        <v>2.75</v>
-      </c>
-      <c r="U19">
-        <v>2.9</v>
-      </c>
-      <c r="V19">
-        <v>1.35</v>
-      </c>
-      <c r="W19">
-        <v>1.07</v>
-      </c>
-      <c r="X19">
-        <v>1.06</v>
-      </c>
-      <c r="Y19">
-        <v>1.37</v>
-      </c>
-      <c r="Z19">
-        <v>2.85</v>
-      </c>
       <c r="AA19">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AB19">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="AC19">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AD19">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE19">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AF19">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="AG19">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK19">
-        <v>1.35</v>
+        <v>1.7</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,64 +3569,64 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="O20">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="P20">
-        <v>4.54</v>
+        <v>4.15</v>
       </c>
       <c r="Q20">
-        <v>2.41</v>
+        <v>2.22</v>
       </c>
       <c r="R20">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="S20">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="T20">
-        <v>2.47</v>
+        <v>2.66</v>
       </c>
       <c r="U20">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="V20">
         <v>1.31</v>
       </c>
       <c r="W20">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X20">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y20">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Z20">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="AA20">
         <v>2.15</v>
       </c>
       <c r="AB20">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC20">
         <v>4.1</v>
       </c>
       <c r="AD20">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE20">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AF20">
-        <v>2.01</v>
+        <v>2</v>
       </c>
       <c r="AG20">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3642,7 +3642,7 @@
         <v>1.29</v>
       </c>
       <c r="AK20">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.48</v>
+        <v>1.29</v>
       </c>
       <c r="O21">
         <v>4.2</v>
       </c>
       <c r="P21">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="Q21">
         <v>1.91</v>
@@ -3774,7 +3774,7 @@
         <v>1.73</v>
       </c>
       <c r="AB21">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="AC21">
         <v>2.35</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -2600,13 +2600,13 @@
         <v>5.5</v>
       </c>
       <c r="Q14">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="R14">
         <v>2.14</v>
       </c>
       <c r="S14">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="T14">
         <v>2.44</v>
@@ -2621,7 +2621,7 @@
         <v>1</v>
       </c>
       <c r="X14">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y14">
         <v>1.42</v>
@@ -2636,7 +2636,7 @@
         <v>1.58</v>
       </c>
       <c r="AC14">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AD14">
         <v>1.2</v>
@@ -2769,7 +2769,7 @@
         <v>2.07</v>
       </c>
       <c r="S15">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="T15">
         <v>2.36</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
+        <v>2.08</v>
+      </c>
+      <c r="O17">
+        <v>3.3</v>
+      </c>
+      <c r="P17">
+        <v>3.75</v>
+      </c>
+      <c r="Q17">
+        <v>2.6</v>
+      </c>
+      <c r="R17">
+        <v>2.05</v>
+      </c>
+      <c r="S17">
+        <v>1.4</v>
+      </c>
+      <c r="T17">
+        <v>2.7</v>
+      </c>
+      <c r="U17">
         <v>3.1</v>
       </c>
-      <c r="O17">
-        <v>3.2</v>
-      </c>
-      <c r="P17">
-        <v>2.37</v>
-      </c>
-      <c r="Q17">
-        <v>3.75</v>
-      </c>
-      <c r="R17">
-        <v>2.2</v>
-      </c>
-      <c r="S17">
-        <v>1.42</v>
-      </c>
-      <c r="T17">
-        <v>2.65</v>
-      </c>
-      <c r="U17">
-        <v>2.8</v>
-      </c>
       <c r="V17">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
+        <v>1.05</v>
+      </c>
+      <c r="Y17">
+        <v>1.33</v>
+      </c>
+      <c r="Z17">
+        <v>3.05</v>
+      </c>
+      <c r="AA17">
+        <v>2.16</v>
+      </c>
+      <c r="AB17">
+        <v>1.68</v>
+      </c>
+      <c r="AC17">
+        <v>3.95</v>
+      </c>
+      <c r="AD17">
+        <v>1.23</v>
+      </c>
+      <c r="AE17">
         <v>1.04</v>
       </c>
-      <c r="Y17">
-        <v>1.28</v>
-      </c>
-      <c r="Z17">
-        <v>3.4</v>
-      </c>
-      <c r="AA17">
-        <v>2</v>
-      </c>
-      <c r="AB17">
+      <c r="AF17">
         <v>1.85</v>
       </c>
-      <c r="AC17">
-        <v>3.6</v>
-      </c>
-      <c r="AD17">
-        <v>1.33</v>
-      </c>
-      <c r="AE17">
-        <v>1.1</v>
-      </c>
-      <c r="AF17">
-        <v>1.83</v>
-      </c>
       <c r="AG17">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AK17">
-        <v>1.37</v>
+        <v>1.75</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.08</v>
+        <v>3.14</v>
       </c>
       <c r="O18">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P18">
+        <v>2.37</v>
+      </c>
+      <c r="Q18">
         <v>3.75</v>
       </c>
-      <c r="Q18">
-        <v>2.6</v>
-      </c>
       <c r="R18">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S18">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T18">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="U18">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="V18">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W18">
+        <v>1.07</v>
+      </c>
+      <c r="X18">
         <v>1.04</v>
       </c>
-      <c r="X18">
-        <v>1.05</v>
-      </c>
       <c r="Y18">
+        <v>1.28</v>
+      </c>
+      <c r="Z18">
+        <v>3.4</v>
+      </c>
+      <c r="AA18">
+        <v>2</v>
+      </c>
+      <c r="AB18">
+        <v>1.85</v>
+      </c>
+      <c r="AC18">
+        <v>3.6</v>
+      </c>
+      <c r="AD18">
         <v>1.33</v>
       </c>
-      <c r="Z18">
-        <v>3.05</v>
-      </c>
-      <c r="AA18">
-        <v>2.16</v>
-      </c>
-      <c r="AB18">
-        <v>1.68</v>
-      </c>
-      <c r="AC18">
-        <v>3.95</v>
-      </c>
-      <c r="AD18">
-        <v>1.23</v>
-      </c>
       <c r="AE18">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF18">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG18">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AK18">
-        <v>1.75</v>
+        <v>1.37</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3569,28 +3569,28 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.71</v>
+        <v>1.79</v>
       </c>
       <c r="O20">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P20">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="Q20">
-        <v>2.22</v>
+        <v>2.49</v>
       </c>
       <c r="R20">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="S20">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="T20">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="U20">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="V20">
         <v>1.31</v>
@@ -3602,16 +3602,16 @@
         <v>1.04</v>
       </c>
       <c r="Y20">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="Z20">
-        <v>2.92</v>
+        <v>2.89</v>
       </c>
       <c r="AA20">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AB20">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AC20">
         <v>4.1</v>
@@ -3626,7 +3626,7 @@
         <v>2</v>
       </c>
       <c r="AG20">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK20">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3728,7 +3728,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N21">

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.08</v>
+        <v>3.14</v>
       </c>
       <c r="O17">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P17">
+        <v>2.37</v>
+      </c>
+      <c r="Q17">
         <v>3.75</v>
       </c>
-      <c r="Q17">
-        <v>2.6</v>
-      </c>
       <c r="R17">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S17">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T17">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="U17">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="V17">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W17">
+        <v>1.07</v>
+      </c>
+      <c r="X17">
         <v>1.04</v>
       </c>
-      <c r="X17">
-        <v>1.05</v>
-      </c>
       <c r="Y17">
+        <v>1.28</v>
+      </c>
+      <c r="Z17">
+        <v>3.4</v>
+      </c>
+      <c r="AA17">
+        <v>2</v>
+      </c>
+      <c r="AB17">
+        <v>1.85</v>
+      </c>
+      <c r="AC17">
+        <v>3.6</v>
+      </c>
+      <c r="AD17">
         <v>1.33</v>
       </c>
-      <c r="Z17">
-        <v>3.05</v>
-      </c>
-      <c r="AA17">
-        <v>2.16</v>
-      </c>
-      <c r="AB17">
-        <v>1.68</v>
-      </c>
-      <c r="AC17">
-        <v>3.95</v>
-      </c>
-      <c r="AD17">
-        <v>1.23</v>
-      </c>
       <c r="AE17">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF17">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG17">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AK17">
-        <v>1.75</v>
+        <v>1.37</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G18">
@@ -3239,68 +3239,68 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N18">
-        <v>3.14</v>
+        <v>2.1</v>
       </c>
       <c r="O18">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P18">
-        <v>2.37</v>
+        <v>3.4</v>
       </c>
       <c r="Q18">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="R18">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S18">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T18">
         <v>2.65</v>
       </c>
       <c r="U18">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V18">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W18">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X18">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y18">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z18">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AA18">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AB18">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC18">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AD18">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AE18">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF18">
         <v>1.83</v>
       </c>
       <c r="AG18">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3313,10 +3313,10 @@
         </is>
       </c>
       <c r="AJ18">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AK18">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G19">
@@ -3402,68 +3402,68 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N19">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="O19">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P19">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="Q19">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="R19">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S19">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T19">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="U19">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="V19">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W19">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X19">
         <v>1.05</v>
       </c>
       <c r="Y19">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z19">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA19">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="AB19">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC19">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AD19">
         <v>1.23</v>
       </c>
       <c r="AE19">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF19">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG19">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3479,7 +3479,7 @@
         <v>1.3</v>
       </c>
       <c r="AK19">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL19">
         <v>0</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -635,80 +635,80 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="O2">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P2">
-        <v>5.3</v>
+        <v>5.87</v>
       </c>
       <c r="Q2">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="R2">
-        <v>2.19</v>
+        <v>1.95</v>
       </c>
       <c r="S2">
+        <v>1.45</v>
+      </c>
+      <c r="T2">
+        <v>2.36</v>
+      </c>
+      <c r="U2">
+        <v>3.28</v>
+      </c>
+      <c r="V2">
+        <v>1.26</v>
+      </c>
+      <c r="W2">
+        <v>1.06</v>
+      </c>
+      <c r="X2">
+        <v>1.04</v>
+      </c>
+      <c r="Y2">
         <v>1.4</v>
       </c>
-      <c r="T2">
-        <v>2.65</v>
-      </c>
-      <c r="U2">
-        <v>3.06</v>
-      </c>
-      <c r="V2">
-        <v>1.3</v>
-      </c>
-      <c r="W2">
-        <v>1.07</v>
-      </c>
-      <c r="X2">
-        <v>1.03</v>
-      </c>
-      <c r="Y2">
-        <v>1.35</v>
-      </c>
       <c r="Z2">
-        <v>3.01</v>
+        <v>2.88</v>
       </c>
       <c r="AA2">
+        <v>2.25</v>
+      </c>
+      <c r="AB2">
+        <v>1.57</v>
+      </c>
+      <c r="AC2">
+        <v>4.33</v>
+      </c>
+      <c r="AD2">
+        <v>1.2</v>
+      </c>
+      <c r="AE2">
+        <v>1.06</v>
+      </c>
+      <c r="AF2">
+        <v>2.18</v>
+      </c>
+      <c r="AG2">
+        <v>1.58</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ2">
+        <v>1.27</v>
+      </c>
+      <c r="AK2">
         <v>2.11</v>
-      </c>
-      <c r="AB2">
-        <v>1.68</v>
-      </c>
-      <c r="AC2">
-        <v>4.34</v>
-      </c>
-      <c r="AD2">
-        <v>1.22</v>
-      </c>
-      <c r="AE2">
-        <v>1.03</v>
-      </c>
-      <c r="AF2">
-        <v>2</v>
-      </c>
-      <c r="AG2">
-        <v>1.7</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2">
-        <v>1.11</v>
-      </c>
-      <c r="AK2">
-        <v>2.2</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -798,58 +798,58 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="O3">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P3">
-        <v>3.6</v>
+        <v>3.69</v>
       </c>
       <c r="Q3">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="R3">
-        <v>2.07</v>
+        <v>1.92</v>
       </c>
       <c r="S3">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="T3">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="U3">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="V3">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="W3">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X3">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y3">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="Z3">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="AA3">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
       <c r="AB3">
         <v>1.62</v>
       </c>
       <c r="AC3">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="AD3">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE3">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF3">
         <v>1.93</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK3">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -961,25 +961,25 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.76</v>
+        <v>1.69</v>
       </c>
       <c r="O4">
-        <v>3.57</v>
+        <v>3.3</v>
       </c>
       <c r="P4">
-        <v>4.46</v>
+        <v>3.45</v>
       </c>
       <c r="Q4">
-        <v>2.27</v>
+        <v>2.24</v>
       </c>
       <c r="R4">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S4">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="T4">
-        <v>2.52</v>
+        <v>2.75</v>
       </c>
       <c r="U4">
         <v>2.92</v>
@@ -988,37 +988,37 @@
         <v>1.32</v>
       </c>
       <c r="W4">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y4">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="Z4">
         <v>3.25</v>
       </c>
       <c r="AA4">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB4">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AC4">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="AD4">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE4">
         <v>1.04</v>
       </c>
       <c r="AF4">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AG4">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>1.17</v>
       </c>
       <c r="AK4">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -1124,64 +1124,64 @@
         </is>
       </c>
       <c r="N5">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="O5">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="P5">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Q5">
-        <v>3.72</v>
+        <v>3.65</v>
       </c>
       <c r="R5">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S5">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="T5">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="U5">
-        <v>2.73</v>
+        <v>2.53</v>
       </c>
       <c r="V5">
         <v>1.42</v>
       </c>
       <c r="W5">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y5">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="Z5">
-        <v>3.38</v>
+        <v>3.54</v>
       </c>
       <c r="AA5">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AB5">
-        <v>1.85</v>
+        <v>1.96</v>
       </c>
       <c r="AC5">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="AD5">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AE5">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF5">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="AG5">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1194,10 +1194,10 @@
         </is>
       </c>
       <c r="AJ5">
-        <v>1.3</v>
+        <v>1.64</v>
       </c>
       <c r="AK5">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1287,61 +1287,61 @@
         </is>
       </c>
       <c r="N6">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="O6">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="P6">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="Q6">
-        <v>5.73</v>
+        <v>5.65</v>
       </c>
       <c r="R6">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="S6">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="T6">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="U6">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="V6">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="W6">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X6">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y6">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Z6">
-        <v>3.62</v>
+        <v>4.2</v>
       </c>
       <c r="AA6">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AB6">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="AC6">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="AD6">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="AE6">
         <v>1.15</v>
       </c>
       <c r="AF6">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AG6">
         <v>1.83</v>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="AJ6">
-        <v>2.61</v>
+        <v>1.2</v>
       </c>
       <c r="AK6">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AL6">
         <v>0</v>
@@ -1450,34 +1450,34 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="O7">
         <v>3.55</v>
       </c>
       <c r="P7">
-        <v>2.12</v>
+        <v>1.97</v>
       </c>
       <c r="Q7">
-        <v>3.77</v>
+        <v>3.65</v>
       </c>
       <c r="R7">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S7">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="T7">
         <v>3.3</v>
       </c>
       <c r="U7">
-        <v>2.41</v>
+        <v>2.54</v>
       </c>
       <c r="V7">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="W7">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="X7">
         <v>1.02</v>
@@ -1486,16 +1486,16 @@
         <v>1.21</v>
       </c>
       <c r="Z7">
-        <v>4.29</v>
+        <v>4.1</v>
       </c>
       <c r="AA7">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="AB7">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AC7">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="AD7">
         <v>1.4</v>
@@ -1504,10 +1504,10 @@
         <v>1.13</v>
       </c>
       <c r="AF7">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AG7">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1523,7 +1523,7 @@
         <v>1.26</v>
       </c>
       <c r="AK7">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,34 +1613,34 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.16</v>
+        <v>2.23</v>
       </c>
       <c r="O8">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="P8">
-        <v>2.48</v>
+        <v>2.82</v>
       </c>
       <c r="Q8">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="R8">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="S8">
         <v>1.25</v>
       </c>
       <c r="T8">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="U8">
         <v>2.39</v>
       </c>
       <c r="V8">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="W8">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="X8">
         <v>1.01</v>
@@ -1649,10 +1649,10 @@
         <v>1.2</v>
       </c>
       <c r="Z8">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="AA8">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="AB8">
         <v>2.25</v>
@@ -1661,16 +1661,16 @@
         <v>2.46</v>
       </c>
       <c r="AD8">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AE8">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="AF8">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AG8">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1683,10 +1683,10 @@
         </is>
       </c>
       <c r="AJ8">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,13 +1776,13 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="O9">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="P9">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Q9">
         <v>1.75</v>
@@ -1794,16 +1794,16 @@
         <v>1.25</v>
       </c>
       <c r="T9">
-        <v>3.42</v>
+        <v>3.5</v>
       </c>
       <c r="U9">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="V9">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="W9">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X9">
         <v>1.01</v>
@@ -1812,25 +1812,25 @@
         <v>1.14</v>
       </c>
       <c r="Z9">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AA9">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AB9">
-        <v>2.25</v>
+        <v>2.34</v>
       </c>
       <c r="AC9">
         <v>2.49</v>
       </c>
       <c r="AD9">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="AE9">
         <v>1.15</v>
       </c>
       <c r="AF9">
-        <v>1.8</v>
+        <v>1.77</v>
       </c>
       <c r="AG9">
         <v>1.9</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="AJ9">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AK9">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1942,61 +1942,61 @@
         <v>1.48</v>
       </c>
       <c r="O10">
-        <v>4.05</v>
+        <v>4.1</v>
       </c>
       <c r="P10">
-        <v>5.15</v>
+        <v>5.54</v>
       </c>
       <c r="Q10">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="R10">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="S10">
         <v>1.25</v>
       </c>
       <c r="T10">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="U10">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="V10">
         <v>1.55</v>
       </c>
       <c r="W10">
-        <v>1.12</v>
+        <v>1.09</v>
       </c>
       <c r="X10">
         <v>1.01</v>
       </c>
       <c r="Y10">
+        <v>1.17</v>
+      </c>
+      <c r="Z10">
+        <v>4.33</v>
+      </c>
+      <c r="AA10">
+        <v>1.58</v>
+      </c>
+      <c r="AB10">
+        <v>2.26</v>
+      </c>
+      <c r="AC10">
+        <v>2.49</v>
+      </c>
+      <c r="AD10">
+        <v>1.49</v>
+      </c>
+      <c r="AE10">
         <v>1.15</v>
-      </c>
-      <c r="Z10">
-        <v>4.3</v>
-      </c>
-      <c r="AA10">
-        <v>1.7</v>
-      </c>
-      <c r="AB10">
-        <v>2.06</v>
-      </c>
-      <c r="AC10">
-        <v>2.55</v>
-      </c>
-      <c r="AD10">
-        <v>1.41</v>
-      </c>
-      <c r="AE10">
-        <v>1.2</v>
       </c>
       <c r="AF10">
         <v>1.67</v>
       </c>
       <c r="AG10">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="AK10">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="O11">
-        <v>4.45</v>
+        <v>4.75</v>
       </c>
       <c r="P11">
-        <v>6.3</v>
+        <v>7.4</v>
       </c>
       <c r="Q11">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="R11">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="S11">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="T11">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="U11">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="V11">
         <v>1.54</v>
       </c>
       <c r="W11">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="X11">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y11">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="Z11">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA11">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AB11">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="AC11">
-        <v>2.39</v>
+        <v>2.6</v>
       </c>
       <c r="AD11">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="AE11">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AF11">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="AG11">
-        <v>1.82</v>
+        <v>1.84</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="AJ11">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AK11">
-        <v>2.59</v>
+        <v>3.05</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,64 +2265,64 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="O12">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="P12">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="Q12">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="R12">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="S12">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T12">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="U12">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="V12">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="W12">
         <v>1.14</v>
       </c>
       <c r="X12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y12">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z12">
-        <v>4.8</v>
+        <v>4.75</v>
       </c>
       <c r="AA12">
         <v>1.57</v>
       </c>
       <c r="AB12">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="AC12">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="AD12">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AE12">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AF12">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG12">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="AJ12">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AK12">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,65 +2428,65 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="O13">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="P13">
-        <v>4.07</v>
+        <v>3.81</v>
       </c>
       <c r="Q13">
+        <v>2.38</v>
+      </c>
+      <c r="R13">
         <v>2.3</v>
-      </c>
-      <c r="R13">
-        <v>2.25</v>
       </c>
       <c r="S13">
         <v>1.3</v>
       </c>
       <c r="T13">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="U13">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="V13">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="W13">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="X13">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y13">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="Z13">
-        <v>4.33</v>
+        <v>3.8</v>
       </c>
       <c r="AA13">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="AB13">
+        <v>2.1</v>
+      </c>
+      <c r="AC13">
+        <v>2.64</v>
+      </c>
+      <c r="AD13">
+        <v>1.38</v>
+      </c>
+      <c r="AE13">
+        <v>1.12</v>
+      </c>
+      <c r="AF13">
+        <v>1.65</v>
+      </c>
+      <c r="AG13">
         <v>2.05</v>
       </c>
-      <c r="AC13">
-        <v>2.68</v>
-      </c>
-      <c r="AD13">
-        <v>1.4</v>
-      </c>
-      <c r="AE13">
-        <v>1.14</v>
-      </c>
-      <c r="AF13">
-        <v>1.7</v>
-      </c>
-      <c r="AG13">
-        <v>1.98</v>
-      </c>
       <c r="AH13" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AK13">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2594,34 +2594,34 @@
         <v>1.53</v>
       </c>
       <c r="O14">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="P14">
-        <v>5.5</v>
+        <v>5.25</v>
       </c>
       <c r="Q14">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="R14">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="S14">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="T14">
         <v>2.44</v>
       </c>
       <c r="U14">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="V14">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W14">
         <v>1</v>
       </c>
       <c r="X14">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y14">
         <v>1.42</v>
@@ -2636,13 +2636,13 @@
         <v>1.58</v>
       </c>
       <c r="AC14">
-        <v>4.5</v>
+        <v>4.25</v>
       </c>
       <c r="AD14">
         <v>1.2</v>
       </c>
       <c r="AE14">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF14">
         <v>2.15</v>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK14">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2766,22 +2766,22 @@
         <v>4.2</v>
       </c>
       <c r="R15">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="S15">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="T15">
         <v>2.36</v>
       </c>
       <c r="U15">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="V15">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="W15">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X15">
         <v>1.05</v>
@@ -2790,13 +2790,13 @@
         <v>1.36</v>
       </c>
       <c r="Z15">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="AA15">
-        <v>2.35</v>
+        <v>2.17</v>
       </c>
       <c r="AB15">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="AC15">
         <v>4.1</v>
@@ -2805,7 +2805,7 @@
         <v>1.21</v>
       </c>
       <c r="AE15">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF15">
         <v>1.88</v>
@@ -2824,7 +2824,7 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.61</v>
+        <v>1.33</v>
       </c>
       <c r="AK15">
         <v>1.21</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G17">
@@ -3076,68 +3076,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N17">
-        <v>3.14</v>
+        <v>2.1</v>
       </c>
       <c r="O17">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P17">
-        <v>2.37</v>
+        <v>3.4</v>
       </c>
       <c r="Q17">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="R17">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S17">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T17">
         <v>2.65</v>
       </c>
       <c r="U17">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V17">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X17">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y17">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z17">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AA17">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="AB17">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC17">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AD17">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AE17">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AF17">
         <v>1.83</v>
       </c>
       <c r="AG17">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3150,10 +3150,10 @@
         </is>
       </c>
       <c r="AJ17">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AK17">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G18">
@@ -3239,68 +3239,68 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N18">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="O18">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P18">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="Q18">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="R18">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S18">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T18">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="U18">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="V18">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W18">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X18">
         <v>1.05</v>
       </c>
       <c r="Y18">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z18">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="AA18">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="AB18">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC18">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AD18">
         <v>1.23</v>
       </c>
       <c r="AE18">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF18">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG18">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.3</v>
       </c>
       <c r="AK18">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G19">
@@ -3406,64 +3406,64 @@
         </is>
       </c>
       <c r="N19">
-        <v>2.08</v>
+        <v>3.14</v>
       </c>
       <c r="O19">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P19">
+        <v>2.37</v>
+      </c>
+      <c r="Q19">
         <v>3.75</v>
       </c>
-      <c r="Q19">
-        <v>2.6</v>
-      </c>
       <c r="R19">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S19">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T19">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="U19">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="V19">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W19">
+        <v>1.07</v>
+      </c>
+      <c r="X19">
         <v>1.04</v>
       </c>
-      <c r="X19">
-        <v>1.05</v>
-      </c>
       <c r="Y19">
+        <v>1.28</v>
+      </c>
+      <c r="Z19">
+        <v>3.4</v>
+      </c>
+      <c r="AA19">
+        <v>2</v>
+      </c>
+      <c r="AB19">
+        <v>1.85</v>
+      </c>
+      <c r="AC19">
+        <v>3.6</v>
+      </c>
+      <c r="AD19">
         <v>1.33</v>
       </c>
-      <c r="Z19">
-        <v>3.05</v>
-      </c>
-      <c r="AA19">
-        <v>2.16</v>
-      </c>
-      <c r="AB19">
-        <v>1.68</v>
-      </c>
-      <c r="AC19">
-        <v>3.95</v>
-      </c>
-      <c r="AD19">
-        <v>1.23</v>
-      </c>
       <c r="AE19">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF19">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG19">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="AK19">
-        <v>1.75</v>
+        <v>1.37</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,49 +3569,49 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="O20">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="P20">
         <v>4.2</v>
       </c>
       <c r="Q20">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="R20">
-        <v>2.13</v>
+        <v>2.15</v>
       </c>
       <c r="S20">
         <v>1.46</v>
       </c>
       <c r="T20">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="U20">
         <v>3.2</v>
       </c>
       <c r="V20">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W20">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X20">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y20">
         <v>1.41</v>
       </c>
       <c r="Z20">
-        <v>2.89</v>
+        <v>2.93</v>
       </c>
       <c r="AA20">
         <v>2.2</v>
       </c>
       <c r="AB20">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC20">
         <v>4.1</v>
@@ -3732,13 +3732,13 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.29</v>
+        <v>1.39</v>
       </c>
       <c r="O21">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="P21">
-        <v>5.5</v>
+        <v>5.69</v>
       </c>
       <c r="Q21">
         <v>1.91</v>
@@ -3750,25 +3750,25 @@
         <v>1.25</v>
       </c>
       <c r="T21">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="U21">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="V21">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="W21">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="X21">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y21">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="Z21">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA21">
         <v>1.73</v>
@@ -3777,13 +3777,13 @@
         <v>2.37</v>
       </c>
       <c r="AC21">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AD21">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AE21">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AF21">
         <v>1.88</v>
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AK21">
         <v>2.43</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -603,12 +603,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G2">
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="O2">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="P2">
-        <v>5.87</v>
+        <v>3.69</v>
       </c>
       <c r="Q2">
-        <v>2.21</v>
+        <v>2.7</v>
       </c>
       <c r="R2">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="S2">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="T2">
-        <v>2.36</v>
+        <v>2.62</v>
       </c>
       <c r="U2">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="V2">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W2">
+        <v>1.05</v>
+      </c>
+      <c r="X2">
         <v>1.06</v>
       </c>
-      <c r="X2">
-        <v>1.04</v>
-      </c>
       <c r="Y2">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="Z2">
         <v>2.88</v>
       </c>
       <c r="AA2">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AB2">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AC2">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AD2">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE2">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="AF2">
-        <v>2.18</v>
+        <v>1.93</v>
       </c>
       <c r="AG2">
-        <v>1.58</v>
+        <v>1.78</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AK2">
-        <v>2.11</v>
+        <v>1.65</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G3">
@@ -798,31 +798,31 @@
         </is>
       </c>
       <c r="N3">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="O3">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="P3">
-        <v>3.69</v>
+        <v>3.45</v>
       </c>
       <c r="Q3">
-        <v>2.7</v>
+        <v>2.24</v>
       </c>
       <c r="R3">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="S3">
         <v>1.4</v>
       </c>
       <c r="T3">
-        <v>2.62</v>
+        <v>2.75</v>
       </c>
       <c r="U3">
-        <v>3.14</v>
+        <v>2.92</v>
       </c>
       <c r="V3">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="W3">
         <v>1.05</v>
@@ -831,31 +831,31 @@
         <v>1.06</v>
       </c>
       <c r="Y3">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="Z3">
-        <v>2.88</v>
+        <v>3.25</v>
       </c>
       <c r="AA3">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="AB3">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AC3">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AD3">
         <v>1.22</v>
       </c>
       <c r="AE3">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="AF3">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AG3">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.3</v>
+        <v>1.17</v>
       </c>
       <c r="AK3">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.69</v>
+        <v>1.61</v>
       </c>
       <c r="O4">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="P4">
-        <v>3.45</v>
+        <v>5.87</v>
       </c>
       <c r="Q4">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="R4">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="S4">
+        <v>1.45</v>
+      </c>
+      <c r="T4">
+        <v>2.36</v>
+      </c>
+      <c r="U4">
+        <v>3.28</v>
+      </c>
+      <c r="V4">
+        <v>1.26</v>
+      </c>
+      <c r="W4">
+        <v>1.06</v>
+      </c>
+      <c r="X4">
+        <v>1.04</v>
+      </c>
+      <c r="Y4">
         <v>1.4</v>
       </c>
-      <c r="T4">
-        <v>2.75</v>
-      </c>
-      <c r="U4">
-        <v>2.92</v>
-      </c>
-      <c r="V4">
-        <v>1.32</v>
-      </c>
-      <c r="W4">
-        <v>1.05</v>
-      </c>
-      <c r="X4">
+      <c r="Z4">
+        <v>2.88</v>
+      </c>
+      <c r="AA4">
+        <v>2.25</v>
+      </c>
+      <c r="AB4">
+        <v>1.57</v>
+      </c>
+      <c r="AC4">
+        <v>4.33</v>
+      </c>
+      <c r="AD4">
+        <v>1.2</v>
+      </c>
+      <c r="AE4">
         <v>1.06</v>
       </c>
-      <c r="Y4">
-        <v>1.31</v>
-      </c>
-      <c r="Z4">
-        <v>3.25</v>
-      </c>
-      <c r="AA4">
-        <v>2.03</v>
-      </c>
-      <c r="AB4">
-        <v>1.73</v>
-      </c>
-      <c r="AC4">
-        <v>4.1</v>
-      </c>
-      <c r="AD4">
-        <v>1.22</v>
-      </c>
-      <c r="AE4">
-        <v>1.04</v>
-      </c>
       <c r="AF4">
-        <v>1.88</v>
+        <v>2.18</v>
       </c>
       <c r="AG4">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AK4">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -2953,22 +2953,22 @@
         <v>1.33</v>
       </c>
       <c r="Z16">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="AA16">
         <v>1.92</v>
       </c>
       <c r="AB16">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AC16">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="AD16">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AE16">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AF16">
         <v>1.87</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bragantino</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G17">
@@ -3076,68 +3076,68 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N17">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="O17">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="P17">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="Q17">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="R17">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S17">
         <v>1.44</v>
       </c>
       <c r="T17">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="U17">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="V17">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W17">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X17">
         <v>1.05</v>
       </c>
       <c r="Y17">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="Z17">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="AA17">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="AB17">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AC17">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AD17">
         <v>1.23</v>
       </c>
       <c r="AE17">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AF17">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG17">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.3</v>
       </c>
       <c r="AK17">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.08</v>
+        <v>3.1</v>
       </c>
       <c r="O18">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P18">
+        <v>2.37</v>
+      </c>
+      <c r="Q18">
         <v>3.75</v>
       </c>
-      <c r="Q18">
-        <v>2.6</v>
-      </c>
       <c r="R18">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S18">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T18">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="U18">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="V18">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W18">
+        <v>1.07</v>
+      </c>
+      <c r="X18">
         <v>1.04</v>
       </c>
-      <c r="X18">
-        <v>1.05</v>
-      </c>
       <c r="Y18">
+        <v>1.28</v>
+      </c>
+      <c r="Z18">
+        <v>3.4</v>
+      </c>
+      <c r="AA18">
+        <v>2</v>
+      </c>
+      <c r="AB18">
+        <v>1.85</v>
+      </c>
+      <c r="AC18">
+        <v>3.6</v>
+      </c>
+      <c r="AD18">
         <v>1.33</v>
       </c>
-      <c r="Z18">
-        <v>3.05</v>
-      </c>
-      <c r="AA18">
-        <v>2.16</v>
-      </c>
-      <c r="AB18">
-        <v>1.68</v>
-      </c>
-      <c r="AC18">
-        <v>3.95</v>
-      </c>
-      <c r="AD18">
-        <v>1.23</v>
-      </c>
       <c r="AE18">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF18">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG18">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.3</v>
       </c>
       <c r="AK18">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="AL18">
         <v>0</v>
@@ -3374,12 +3374,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Bragantino</t>
         </is>
       </c>
       <c r="G19">
@@ -3402,68 +3402,68 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="N19">
-        <v>3.14</v>
+        <v>2.1</v>
       </c>
       <c r="O19">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="P19">
-        <v>2.37</v>
+        <v>3.42</v>
       </c>
       <c r="Q19">
-        <v>3.75</v>
+        <v>2.75</v>
       </c>
       <c r="R19">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S19">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T19">
         <v>2.65</v>
       </c>
       <c r="U19">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="V19">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W19">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="X19">
         <v>1.04</v>
       </c>
       <c r="Y19">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="Z19">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="AA19">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AB19">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC19">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="AD19">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE19">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF19">
         <v>1.83</v>
       </c>
       <c r="AG19">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
@@ -3476,10 +3476,10 @@
         </is>
       </c>
       <c r="AJ19">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="AK19">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="AL19">
         <v>0</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -635,64 +635,64 @@
         </is>
       </c>
       <c r="N2">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="O2">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="P2">
-        <v>3.69</v>
+        <v>3.5</v>
       </c>
       <c r="Q2">
         <v>2.7</v>
       </c>
       <c r="R2">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="S2">
         <v>1.4</v>
       </c>
       <c r="T2">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="U2">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="V2">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W2">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X2">
+        <v>1.03</v>
+      </c>
+      <c r="Y2">
+        <v>1.34</v>
+      </c>
+      <c r="Z2">
+        <v>2.86</v>
+      </c>
+      <c r="AA2">
+        <v>2.15</v>
+      </c>
+      <c r="AB2">
+        <v>1.65</v>
+      </c>
+      <c r="AC2">
+        <v>3.8</v>
+      </c>
+      <c r="AD2">
+        <v>1.2</v>
+      </c>
+      <c r="AE2">
         <v>1.06</v>
       </c>
-      <c r="Y2">
-        <v>1.38</v>
-      </c>
-      <c r="Z2">
-        <v>2.88</v>
-      </c>
-      <c r="AA2">
-        <v>2.2</v>
-      </c>
-      <c r="AB2">
-        <v>1.62</v>
-      </c>
-      <c r="AC2">
-        <v>4.2</v>
-      </c>
-      <c r="AD2">
-        <v>1.22</v>
-      </c>
-      <c r="AE2">
-        <v>1.02</v>
-      </c>
       <c r="AF2">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AG2">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -705,10 +705,10 @@
         </is>
       </c>
       <c r="AJ2">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK2">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -766,12 +766,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Navbahor</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G3">
@@ -798,64 +798,64 @@
         </is>
       </c>
       <c r="N3">
-        <v>1.69</v>
+        <v>1.59</v>
       </c>
       <c r="O3">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="P3">
-        <v>3.45</v>
+        <v>4.7</v>
       </c>
       <c r="Q3">
-        <v>2.24</v>
+        <v>2.08</v>
       </c>
       <c r="R3">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="S3">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T3">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="U3">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="V3">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W3">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X3">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y3">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="Z3">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA3">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="AB3">
         <v>1.73</v>
       </c>
       <c r="AC3">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="AD3">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE3">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF3">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
       <c r="AG3">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="AJ3">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="AK3">
-        <v>1.95</v>
+        <v>2.12</v>
       </c>
       <c r="AL3">
         <v>0</v>
@@ -929,12 +929,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Navbahor</t>
         </is>
       </c>
       <c r="G4">
@@ -961,64 +961,64 @@
         </is>
       </c>
       <c r="N4">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="O4">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="P4">
-        <v>5.87</v>
+        <v>4.1</v>
       </c>
       <c r="Q4">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="R4">
-        <v>1.95</v>
+        <v>2.11</v>
       </c>
       <c r="S4">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="T4">
-        <v>2.36</v>
+        <v>2.71</v>
       </c>
       <c r="U4">
-        <v>3.28</v>
+        <v>2.66</v>
       </c>
       <c r="V4">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="W4">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X4">
+        <v>1.05</v>
+      </c>
+      <c r="Y4">
+        <v>1.3</v>
+      </c>
+      <c r="Z4">
+        <v>3.08</v>
+      </c>
+      <c r="AA4">
+        <v>2</v>
+      </c>
+      <c r="AB4">
+        <v>1.75</v>
+      </c>
+      <c r="AC4">
+        <v>3.5</v>
+      </c>
+      <c r="AD4">
+        <v>1.29</v>
+      </c>
+      <c r="AE4">
         <v>1.04</v>
       </c>
-      <c r="Y4">
-        <v>1.4</v>
-      </c>
-      <c r="Z4">
-        <v>2.88</v>
-      </c>
-      <c r="AA4">
-        <v>2.25</v>
-      </c>
-      <c r="AB4">
-        <v>1.57</v>
-      </c>
-      <c r="AC4">
-        <v>4.33</v>
-      </c>
-      <c r="AD4">
-        <v>1.2</v>
-      </c>
-      <c r="AE4">
-        <v>1.06</v>
-      </c>
       <c r="AF4">
-        <v>2.18</v>
+        <v>1.96</v>
       </c>
       <c r="AG4">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="AJ4">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
       <c r="AK4">
-        <v>2.11</v>
+        <v>2.06</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -3048,12 +3048,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>São Paulo</t>
+          <t>Chapecoense</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Santos</t>
+          <t>Vasco da Gama</t>
         </is>
       </c>
       <c r="G17">
@@ -3080,64 +3080,64 @@
         </is>
       </c>
       <c r="N17">
-        <v>2.08</v>
+        <v>3.1</v>
       </c>
       <c r="O17">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P17">
+        <v>2.37</v>
+      </c>
+      <c r="Q17">
         <v>3.75</v>
       </c>
-      <c r="Q17">
-        <v>2.6</v>
-      </c>
       <c r="R17">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="S17">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="T17">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="U17">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="V17">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="W17">
+        <v>1.07</v>
+      </c>
+      <c r="X17">
         <v>1.04</v>
       </c>
-      <c r="X17">
-        <v>1.05</v>
-      </c>
       <c r="Y17">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Z17">
-        <v>2.85</v>
+        <v>3.4</v>
       </c>
       <c r="AA17">
-        <v>2.16</v>
+        <v>2</v>
       </c>
       <c r="AB17">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AC17">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="AD17">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AE17">
-        <v>1.04</v>
+        <v>1.1</v>
       </c>
       <c r="AF17">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="AG17">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3153,7 +3153,7 @@
         <v>1.3</v>
       </c>
       <c r="AK17">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="AL17">
         <v>0</v>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Chapecoense</t>
+          <t>São Paulo</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vasco da Gama</t>
+          <t>Santos</t>
         </is>
       </c>
       <c r="G18">
@@ -3243,64 +3243,64 @@
         </is>
       </c>
       <c r="N18">
+        <v>2.08</v>
+      </c>
+      <c r="O18">
+        <v>3.3</v>
+      </c>
+      <c r="P18">
+        <v>3.75</v>
+      </c>
+      <c r="Q18">
+        <v>2.6</v>
+      </c>
+      <c r="R18">
+        <v>2.05</v>
+      </c>
+      <c r="S18">
+        <v>1.44</v>
+      </c>
+      <c r="T18">
+        <v>2.6</v>
+      </c>
+      <c r="U18">
         <v>3.1</v>
       </c>
-      <c r="O18">
-        <v>3.2</v>
-      </c>
-      <c r="P18">
-        <v>2.37</v>
-      </c>
-      <c r="Q18">
-        <v>3.75</v>
-      </c>
-      <c r="R18">
-        <v>2.2</v>
-      </c>
-      <c r="S18">
-        <v>1.42</v>
-      </c>
-      <c r="T18">
-        <v>2.65</v>
-      </c>
-      <c r="U18">
-        <v>2.8</v>
-      </c>
       <c r="V18">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W18">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X18">
+        <v>1.05</v>
+      </c>
+      <c r="Y18">
+        <v>1.36</v>
+      </c>
+      <c r="Z18">
+        <v>2.85</v>
+      </c>
+      <c r="AA18">
+        <v>2.16</v>
+      </c>
+      <c r="AB18">
+        <v>1.68</v>
+      </c>
+      <c r="AC18">
+        <v>3.95</v>
+      </c>
+      <c r="AD18">
+        <v>1.23</v>
+      </c>
+      <c r="AE18">
         <v>1.04</v>
       </c>
-      <c r="Y18">
-        <v>1.28</v>
-      </c>
-      <c r="Z18">
-        <v>3.4</v>
-      </c>
-      <c r="AA18">
-        <v>2</v>
-      </c>
-      <c r="AB18">
+      <c r="AF18">
         <v>1.85</v>
       </c>
-      <c r="AC18">
-        <v>3.6</v>
-      </c>
-      <c r="AD18">
-        <v>1.33</v>
-      </c>
-      <c r="AE18">
-        <v>1.1</v>
-      </c>
-      <c r="AF18">
-        <v>1.83</v>
-      </c>
       <c r="AG18">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3316,7 +3316,7 @@
         <v>1.3</v>
       </c>
       <c r="AK18">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AL18">
         <v>0</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -612,13 +612,13 @@
         </is>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -631,7 +631,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2">
@@ -696,7 +696,7 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34"]</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -714,28 +714,28 @@
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN2">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AO2">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP2">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AQ2">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AR2">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AS2">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT2">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         </is>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -787,14 +787,14 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3">
@@ -859,7 +859,7 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["81"]</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -877,28 +877,28 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AN3">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO3">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP3">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AQ3">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AR3">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="AS3">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AT3">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
@@ -938,26 +938,26 @@
         </is>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4">
@@ -1022,12 +1022,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["90+8"]</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["3"]</t>
         </is>
       </c>
       <c r="AJ4">
@@ -1040,28 +1040,28 @@
         <v>0</v>
       </c>
       <c r="AM4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN4">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP4">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ4">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AR4">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS4">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AT4">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -1116,24 +1116,24 @@
         <v>0</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="O5">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="P5">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q5">
-        <v>3.65</v>
+        <v>3.32</v>
       </c>
       <c r="R5">
         <v>2.25</v>
@@ -1142,16 +1142,16 @@
         <v>1.34</v>
       </c>
       <c r="T5">
-        <v>2.78</v>
+        <v>2.73</v>
       </c>
       <c r="U5">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="V5">
         <v>1.42</v>
       </c>
       <c r="W5">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X5">
         <v>1.04</v>
@@ -1160,25 +1160,25 @@
         <v>1.24</v>
       </c>
       <c r="Z5">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="AA5">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="AB5">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AC5">
         <v>2.91</v>
       </c>
       <c r="AD5">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE5">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="AF5">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AG5">
         <v>2.1</v>
@@ -1190,41 +1190,41 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["52", "70"]</t>
         </is>
       </c>
       <c r="AJ5">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AK5">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AL5">
         <v>0</v>
       </c>
       <c r="AM5">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN5">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ5">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AR5">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AS5">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="AT5">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
@@ -1283,68 +1283,68 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6">
-        <v>4.6</v>
+        <v>5.65</v>
       </c>
       <c r="O6">
-        <v>4.1</v>
+        <v>4.45</v>
       </c>
       <c r="P6">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="Q6">
-        <v>5.65</v>
+        <v>5</v>
       </c>
       <c r="R6">
         <v>2.45</v>
       </c>
       <c r="S6">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="T6">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="U6">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="V6">
-        <v>1.47</v>
+        <v>1.53</v>
       </c>
       <c r="W6">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X6">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y6">
         <v>1.22</v>
       </c>
       <c r="Z6">
-        <v>4.2</v>
+        <v>3.98</v>
       </c>
       <c r="AA6">
+        <v>1.68</v>
+      </c>
+      <c r="AB6">
+        <v>2</v>
+      </c>
+      <c r="AC6">
+        <v>2.8</v>
+      </c>
+      <c r="AD6">
+        <v>1.37</v>
+      </c>
+      <c r="AE6">
+        <v>1.13</v>
+      </c>
+      <c r="AF6">
         <v>1.75</v>
       </c>
-      <c r="AB6">
-        <v>1.96</v>
-      </c>
-      <c r="AC6">
-        <v>2.88</v>
-      </c>
-      <c r="AD6">
-        <v>1.4</v>
-      </c>
-      <c r="AE6">
-        <v>1.15</v>
-      </c>
-      <c r="AF6">
-        <v>1.83</v>
-      </c>
       <c r="AG6">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1360,34 +1360,34 @@
         <v>1.2</v>
       </c>
       <c r="AK6">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AL6">
         <v>0</v>
       </c>
       <c r="AM6">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP6">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ6">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AR6">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AS6">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="AT6">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
@@ -1450,28 +1450,28 @@
         </is>
       </c>
       <c r="N7">
-        <v>3.15</v>
+        <v>3.01</v>
       </c>
       <c r="O7">
         <v>3.55</v>
       </c>
       <c r="P7">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="Q7">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="R7">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S7">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="T7">
         <v>3.3</v>
       </c>
       <c r="U7">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="V7">
         <v>1.5</v>
@@ -1480,22 +1480,22 @@
         <v>1.08</v>
       </c>
       <c r="X7">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y7">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="Z7">
         <v>4.1</v>
       </c>
       <c r="AA7">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="AB7">
         <v>2.11</v>
       </c>
       <c r="AC7">
-        <v>2.59</v>
+        <v>2.78</v>
       </c>
       <c r="AD7">
         <v>1.4</v>
@@ -1507,7 +1507,7 @@
         <v>1.57</v>
       </c>
       <c r="AG7">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1520,10 +1520,10 @@
         </is>
       </c>
       <c r="AJ7">
-        <v>1.26</v>
+        <v>1.65</v>
       </c>
       <c r="AK7">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AL7">
         <v>0</v>
@@ -1613,31 +1613,31 @@
         </is>
       </c>
       <c r="N8">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="O8">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="P8">
         <v>2.82</v>
       </c>
       <c r="Q8">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="R8">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="S8">
         <v>1.25</v>
       </c>
       <c r="T8">
-        <v>3.1</v>
+        <v>3.22</v>
       </c>
       <c r="U8">
         <v>2.39</v>
       </c>
       <c r="V8">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="W8">
         <v>1.08</v>
@@ -1649,22 +1649,22 @@
         <v>1.2</v>
       </c>
       <c r="Z8">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AA8">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AB8">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AC8">
-        <v>2.46</v>
+        <v>2.59</v>
       </c>
       <c r="AD8">
         <v>1.5</v>
       </c>
       <c r="AE8">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF8">
         <v>1.52</v>
@@ -1686,7 +1686,7 @@
         <v>1.25</v>
       </c>
       <c r="AK8">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AL8">
         <v>0</v>
@@ -1776,80 +1776,80 @@
         </is>
       </c>
       <c r="N9">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="O9">
-        <v>4.9</v>
+        <v>5.19</v>
       </c>
       <c r="P9">
-        <v>6.5</v>
+        <v>7.65</v>
       </c>
       <c r="Q9">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="R9">
         <v>2.5</v>
       </c>
       <c r="S9">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T9">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="U9">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="V9">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="W9">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="X9">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y9">
+        <v>1.12</v>
+      </c>
+      <c r="Z9">
+        <v>4.65</v>
+      </c>
+      <c r="AA9">
+        <v>1.5</v>
+      </c>
+      <c r="AB9">
+        <v>2.48</v>
+      </c>
+      <c r="AC9">
+        <v>2.4</v>
+      </c>
+      <c r="AD9">
+        <v>1.57</v>
+      </c>
+      <c r="AE9">
+        <v>1.2</v>
+      </c>
+      <c r="AF9">
+        <v>1.75</v>
+      </c>
+      <c r="AG9">
+        <v>1.93</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9">
         <v>1.14</v>
       </c>
-      <c r="Z9">
-        <v>4.45</v>
-      </c>
-      <c r="AA9">
-        <v>1.6</v>
-      </c>
-      <c r="AB9">
-        <v>2.34</v>
-      </c>
-      <c r="AC9">
-        <v>2.49</v>
-      </c>
-      <c r="AD9">
-        <v>1.53</v>
-      </c>
-      <c r="AE9">
-        <v>1.15</v>
-      </c>
-      <c r="AF9">
-        <v>1.77</v>
-      </c>
-      <c r="AG9">
-        <v>1.9</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9">
-        <v>1.1</v>
-      </c>
       <c r="AK9">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AL9">
         <v>0</v>
@@ -1939,52 +1939,52 @@
         </is>
       </c>
       <c r="N10">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="O10">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="P10">
-        <v>5.54</v>
+        <v>5.75</v>
       </c>
       <c r="Q10">
         <v>1.91</v>
       </c>
       <c r="R10">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="S10">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="T10">
         <v>3.25</v>
       </c>
       <c r="U10">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="V10">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="W10">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X10">
         <v>1.01</v>
       </c>
       <c r="Y10">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="Z10">
         <v>4.33</v>
       </c>
       <c r="AA10">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AB10">
-        <v>2.26</v>
+        <v>2.23</v>
       </c>
       <c r="AC10">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="AD10">
         <v>1.49</v>
@@ -1993,7 +1993,7 @@
         <v>1.15</v>
       </c>
       <c r="AF10">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AG10">
         <v>2.1</v>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="AJ10">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AK10">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="AL10">
         <v>0</v>
@@ -2102,64 +2102,64 @@
         </is>
       </c>
       <c r="N11">
-        <v>1.37</v>
+        <v>1.44</v>
       </c>
       <c r="O11">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="P11">
-        <v>7.4</v>
+        <v>5.95</v>
       </c>
       <c r="Q11">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="R11">
         <v>2.6</v>
       </c>
       <c r="S11">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="T11">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="U11">
-        <v>2.27</v>
+        <v>2.21</v>
       </c>
       <c r="V11">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="W11">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="X11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y11">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="Z11">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AA11">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AB11">
-        <v>2.28</v>
+        <v>2.35</v>
       </c>
       <c r="AC11">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="AD11">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="AE11">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="AF11">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AG11">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>1.11</v>
       </c>
       <c r="AK11">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="AL11">
         <v>0</v>
@@ -2265,16 +2265,16 @@
         </is>
       </c>
       <c r="N12">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="O12">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="P12">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="Q12">
-        <v>2.21</v>
+        <v>2.35</v>
       </c>
       <c r="R12">
         <v>2.4</v>
@@ -2286,13 +2286,13 @@
         <v>3.7</v>
       </c>
       <c r="U12">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="V12">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="W12">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="X12">
         <v>1.03</v>
@@ -2304,25 +2304,25 @@
         <v>4.75</v>
       </c>
       <c r="AA12">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AB12">
-        <v>2.48</v>
+        <v>2.35</v>
       </c>
       <c r="AC12">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AD12">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="AE12">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AF12">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="AG12">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>1.25</v>
       </c>
       <c r="AK12">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="AL12">
         <v>0</v>
@@ -2428,28 +2428,28 @@
         </is>
       </c>
       <c r="N13">
-        <v>1.82</v>
+        <v>1.6</v>
       </c>
       <c r="O13">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="P13">
-        <v>3.81</v>
+        <v>4.8</v>
       </c>
       <c r="Q13">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="R13">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S13">
         <v>1.3</v>
       </c>
       <c r="T13">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="U13">
-        <v>2.34</v>
+        <v>2.5</v>
       </c>
       <c r="V13">
         <v>1.48</v>
@@ -2461,16 +2461,16 @@
         <v>1</v>
       </c>
       <c r="Y13">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z13">
         <v>3.8</v>
       </c>
       <c r="AA13">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="AB13">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC13">
         <v>2.64</v>
@@ -2479,13 +2479,13 @@
         <v>1.38</v>
       </c>
       <c r="AE13">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AF13">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AG13">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="AJ13">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="AK13">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AL13">
         <v>0</v>
@@ -2591,64 +2591,64 @@
         </is>
       </c>
       <c r="N14">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="O14">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="P14">
         <v>5.25</v>
       </c>
       <c r="Q14">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="R14">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="S14">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="T14">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="U14">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="V14">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W14">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X14">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y14">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="Z14">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="AA14">
         <v>2.31</v>
       </c>
       <c r="AB14">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AC14">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="AD14">
         <v>1.2</v>
       </c>
       <c r="AE14">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF14">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AG14">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2661,10 +2661,10 @@
         </is>
       </c>
       <c r="AJ14">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AK14">
-        <v>2.35</v>
+        <v>2.16</v>
       </c>
       <c r="AL14">
         <v>0</v>
@@ -2754,25 +2754,25 @@
         </is>
       </c>
       <c r="N15">
-        <v>3.6</v>
+        <v>4.06</v>
       </c>
       <c r="O15">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="P15">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="Q15">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="R15">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="S15">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="T15">
-        <v>2.36</v>
+        <v>2.59</v>
       </c>
       <c r="U15">
         <v>3.3</v>
@@ -2784,34 +2784,34 @@
         <v>1.03</v>
       </c>
       <c r="X15">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y15">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="Z15">
-        <v>2.75</v>
+        <v>2.62</v>
       </c>
       <c r="AA15">
         <v>2.17</v>
       </c>
       <c r="AB15">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AC15">
-        <v>4.1</v>
+        <v>4.15</v>
       </c>
       <c r="AD15">
         <v>1.21</v>
       </c>
       <c r="AE15">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF15">
         <v>1.88</v>
       </c>
       <c r="AG15">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2824,10 +2824,10 @@
         </is>
       </c>
       <c r="AJ15">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AK15">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AL15">
         <v>0</v>
@@ -2913,23 +2913,23 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N16">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="O16">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="P16">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Q16">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R16">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="S16">
         <v>1.4</v>
@@ -2938,7 +2938,7 @@
         <v>2.73</v>
       </c>
       <c r="U16">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="V16">
         <v>1.36</v>
@@ -2956,13 +2956,13 @@
         <v>3.3</v>
       </c>
       <c r="AA16">
-        <v>1.92</v>
+        <v>1.79</v>
       </c>
       <c r="AB16">
         <v>1.98</v>
       </c>
       <c r="AC16">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="AD16">
         <v>1.25</v>
@@ -2990,7 +2990,7 @@
         <v>1.29</v>
       </c>
       <c r="AK16">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AL16">
         <v>0</v>
@@ -3095,43 +3095,43 @@
         <v>2.2</v>
       </c>
       <c r="S17">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T17">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="U17">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="V17">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W17">
         <v>1.07</v>
       </c>
       <c r="X17">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y17">
         <v>1.28</v>
       </c>
       <c r="Z17">
-        <v>3.4</v>
+        <v>2.94</v>
       </c>
       <c r="AA17">
         <v>2</v>
       </c>
       <c r="AB17">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AC17">
         <v>3.6</v>
       </c>
       <c r="AD17">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE17">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="AF17">
         <v>1.83</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="N18">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="O18">
         <v>3.3</v>
@@ -3258,28 +3258,28 @@
         <v>2.05</v>
       </c>
       <c r="S18">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T18">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="U18">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="V18">
         <v>1.35</v>
       </c>
       <c r="W18">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X18">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y18">
         <v>1.36</v>
       </c>
       <c r="Z18">
-        <v>2.85</v>
+        <v>2.8</v>
       </c>
       <c r="AA18">
         <v>2.16</v>
@@ -3291,16 +3291,16 @@
         <v>3.95</v>
       </c>
       <c r="AD18">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AE18">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AF18">
         <v>1.85</v>
       </c>
       <c r="AG18">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="N19">
@@ -3412,19 +3412,19 @@
         <v>3.4</v>
       </c>
       <c r="P19">
-        <v>3.42</v>
+        <v>3.4</v>
       </c>
       <c r="Q19">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R19">
         <v>2.1</v>
       </c>
       <c r="S19">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T19">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="U19">
         <v>2.88</v>
@@ -3436,13 +3436,13 @@
         <v>1.05</v>
       </c>
       <c r="X19">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y19">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z19">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="AA19">
         <v>2.15</v>
@@ -3454,10 +3454,10 @@
         <v>3.85</v>
       </c>
       <c r="AD19">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE19">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF19">
         <v>1.83</v>
@@ -3479,7 +3479,7 @@
         <v>1.3</v>
       </c>
       <c r="AK19">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AL19">
         <v>0</v>
@@ -3569,28 +3569,28 @@
         </is>
       </c>
       <c r="N20">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="O20">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="P20">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="Q20">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="R20">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="S20">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="T20">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="U20">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="V20">
         <v>1.32</v>
@@ -3605,22 +3605,22 @@
         <v>1.41</v>
       </c>
       <c r="Z20">
-        <v>2.93</v>
+        <v>2.74</v>
       </c>
       <c r="AA20">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AB20">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AC20">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="AD20">
         <v>1.19</v>
       </c>
       <c r="AE20">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF20">
         <v>2</v>
@@ -3639,10 +3639,10 @@
         </is>
       </c>
       <c r="AJ20">
-        <v>1.3</v>
+        <v>1.16</v>
       </c>
       <c r="AK20">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AL20">
         <v>0</v>
@@ -3732,43 +3732,43 @@
         </is>
       </c>
       <c r="N21">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="O21">
-        <v>4.45</v>
+        <v>4.05</v>
       </c>
       <c r="P21">
-        <v>5.69</v>
+        <v>8.6</v>
       </c>
       <c r="Q21">
         <v>1.91</v>
       </c>
       <c r="R21">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="S21">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T21">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="U21">
-        <v>2.15</v>
+        <v>2.31</v>
       </c>
       <c r="V21">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="W21">
         <v>1.14</v>
       </c>
       <c r="X21">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y21">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="Z21">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="AA21">
         <v>1.73</v>
@@ -3777,16 +3777,16 @@
         <v>2.37</v>
       </c>
       <c r="AC21">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="AD21">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AE21">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AF21">
-        <v>1.88</v>
+        <v>1.69</v>
       </c>
       <c r="AG21">
         <v>1.73</v>
@@ -3802,10 +3802,10 @@
         </is>
       </c>
       <c r="AJ21">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AK21">
-        <v>2.43</v>
+        <v>2.19</v>
       </c>
       <c r="AL21">
         <v>0</v>

--- a/jogos_2026-07-28.xlsx
+++ b/jogos_2026-07-28.xlsx
@@ -1430,13 +1430,13 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["45+2"]</t>
         </is>
       </c>
       <c r="AJ7">
@@ -1529,28 +1529,28 @@
         <v>0</v>
       </c>
       <c r="AM7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN7">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP7">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ7">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AR7">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AS7">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT7">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -1602,14 +1602,14 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["86"]</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["67"]</t>
         </is>
       </c>
       <c r="AJ8">
@@ -1692,28 +1692,28 @@
         <v>0</v>
       </c>
       <c r="AM8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AN8">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>18</v>
       </c>
       <c r="AP8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
@@ -1753,26 +1753,26 @@
         </is>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9">
         <v>0</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L9">
         <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["112", "74", "78"]</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["4", "22"]</t>
         </is>
       </c>
       <c r="AJ9">
@@ -1855,28 +1855,28 @@
         <v>0</v>
       </c>
       <c r="AM9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN9">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>29</v>
       </c>
       <c r="AP9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>0.88</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         </is>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
         <v>0</v>
@@ -1928,14 +1928,14 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
         <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["48"]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -2018,28 +2018,28 @@
         <v>0</v>
       </c>
       <c r="AM10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP10">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>0.82</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
@@ -2079,26 +2079,26 @@
         </is>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11">
@@ -2163,12 +2163,12 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["34", "97"]</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["114", "21"]</t>
         </is>
       </c>
       <c r="AJ11">
@@ -2181,28 +2181,28 @@
         <v>0</v>
       </c>
       <c r="AM11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN11">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP11">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
@@ -2245,7 +2245,7 @@
         <v>0</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -2257,11 +2257,11 @@
         <v>0</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["64", "68"]</t>
         </is>
       </c>
       <c r="AJ12">
@@ -2344,28 +2344,28 @@
         <v>0</v>
       </c>
       <c r="AM12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP12">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
@@ -2405,13 +2405,13 @@
         </is>
       </c>
       <c r="G13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -2420,11 +2420,11 @@
         <v>0</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13">
@@ -2489,12 +2489,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["11", "36"]</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>["73"]</t>
         </is>
       </c>
       <c r="AJ13">
@@ -2507,28 +2507,28 @@
         <v>0</v>
       </c>
       <c r="AM13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AN13">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>15</v>
       </c>
       <c r="AP13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AQ13">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>0.62</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
